--- a/week_2/Input Data.xlsx
+++ b/week_2/Input Data.xlsx
@@ -35,44 +35,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="76">
-  <si>
-    <t>Annual Interest Rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fee</t>
-  </si>
-  <si>
-    <t>Disbursement Date</t>
-  </si>
-  <si>
-    <t>Repayment Frequency</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>Loan Term (Months)</t>
-  </si>
-  <si>
-    <t>Monthly Interest Rate</t>
-  </si>
-  <si>
-    <t>Monthly Interest</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="75">
+  <si>
+    <t>Principal (₦)</t>
   </si>
   <si>
     <t>Monthly payment</t>
   </si>
   <si>
-    <t>Total Payment</t>
-  </si>
-  <si>
-    <t>Principal+Total Interest+Fee</t>
-  </si>
-  <si>
-    <t>Total Interest</t>
-  </si>
-  <si>
     <t>Payment No</t>
   </si>
   <si>
@@ -263,22 +233,58 @@
   </si>
   <si>
     <t>LO16</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Monthly Rate</t>
+  </si>
+  <si>
+    <t>Flat: Total Repayment (₦)</t>
+  </si>
+  <si>
+    <t>Reducing: Total Repayment (₦)</t>
+  </si>
+  <si>
+    <t>Savings with Reducing (₦)</t>
+  </si>
+  <si>
+    <t>Scenario 1</t>
+  </si>
+  <si>
+    <t>Scenario 2</t>
+  </si>
+  <si>
+    <t>Scenario 3</t>
+  </si>
+  <si>
+    <t>months</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="\₦#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -303,8 +309,60 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,6 +373,24 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.24994659260841701"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39994506668294322"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -344,10 +420,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -358,24 +434,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -386,17 +456,53 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -678,502 +784,502 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" style="41" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.36328125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.26953125" style="42" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>51</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>66</v>
+        <v>55</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="I1" t="s">
-        <v>68</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>69</v>
+        <v>58</v>
+      </c>
+      <c r="J1" s="42" t="s">
+        <v>59</v>
       </c>
       <c r="K1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="11">
+        <v>31</v>
+      </c>
+      <c r="C2" s="39">
         <v>50000</v>
       </c>
       <c r="D2" s="2">
         <v>0.48</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="12">
         <v>1000</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="13">
         <v>45840</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I2" s="5">
         <f>D2/12</f>
         <v>0.04</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="42">
         <f>C2*I2*G2+C2+E2</f>
         <v>57000</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="11">
+        <v>32</v>
+      </c>
+      <c r="C3" s="39">
         <v>70000</v>
       </c>
       <c r="D3" s="2">
         <v>0.48</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="12">
         <v>2000</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="13">
         <v>45872</v>
       </c>
       <c r="G3" s="1">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ref="I3:I21" si="0">D3/12</f>
         <v>0.04</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="42">
         <f t="shared" ref="J3:J21" si="1">C3*I3*G3+C3+E3</f>
         <v>80400</v>
       </c>
       <c r="K3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="11">
+        <v>33</v>
+      </c>
+      <c r="C4" s="39">
         <v>90000</v>
       </c>
       <c r="D4" s="2">
         <v>0.48</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="12">
         <v>2000</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="13">
         <v>45842</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I4" s="5">
-        <f t="shared" si="0"/>
+        <f>D4/12</f>
         <v>0.04</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="42">
         <f t="shared" si="1"/>
         <v>102800</v>
       </c>
       <c r="K4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="11">
+        <v>34</v>
+      </c>
+      <c r="C5" s="39">
         <v>110000</v>
       </c>
       <c r="D5" s="2">
         <v>0.48</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>3000</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="13">
         <v>45907</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="42">
         <f t="shared" si="1"/>
         <v>126200</v>
       </c>
       <c r="K5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="11">
+        <v>35</v>
+      </c>
+      <c r="C6" s="39">
         <v>130000</v>
       </c>
       <c r="D6" s="2">
         <v>0.48</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>3000</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="13">
         <v>45938</v>
       </c>
       <c r="G6" s="1">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="42">
         <f t="shared" si="1"/>
         <v>148600</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="11">
+        <v>36</v>
+      </c>
+      <c r="C7" s="39">
         <v>150000</v>
       </c>
       <c r="D7" s="2">
         <v>0.48</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>5000</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="13">
         <v>45847</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="42">
         <f t="shared" si="1"/>
         <v>191000</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="11">
+        <v>37</v>
+      </c>
+      <c r="C8" s="39">
         <v>170000</v>
       </c>
       <c r="D8" s="2">
         <v>0.48</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>2500</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="13">
         <v>45848</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="42">
         <f t="shared" si="1"/>
         <v>192900</v>
       </c>
       <c r="K8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="11">
+        <v>38</v>
+      </c>
+      <c r="C9" s="39">
         <v>60000</v>
       </c>
       <c r="D9" s="2">
         <v>0.48</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>1000</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="13">
         <v>45849</v>
       </c>
       <c r="G9" s="1">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="42">
         <f t="shared" si="1"/>
         <v>68200</v>
       </c>
       <c r="K9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="11">
+        <v>39</v>
+      </c>
+      <c r="C10" s="39">
         <v>80000</v>
       </c>
       <c r="D10" s="2">
         <v>0.48</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>2000</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="13">
         <v>45850</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="42">
         <f t="shared" si="1"/>
         <v>91600</v>
       </c>
       <c r="K10" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="11">
+        <v>40</v>
+      </c>
+      <c r="C11" s="39">
         <v>100000</v>
       </c>
       <c r="D11" s="2">
         <v>0.48</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>3000</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="13">
         <v>45851</v>
       </c>
       <c r="G11" s="1">
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="42">
         <f t="shared" si="1"/>
         <v>115000</v>
       </c>
       <c r="K11" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="11">
+        <v>41</v>
+      </c>
+      <c r="C12" s="39">
         <v>120000</v>
       </c>
       <c r="D12" s="2">
         <v>0.48</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>3000</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="13">
         <v>45852</v>
       </c>
       <c r="G12" s="1">
         <v>12</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="42">
         <f t="shared" si="1"/>
         <v>180600</v>
       </c>
       <c r="K12" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="11">
+        <v>42</v>
+      </c>
+      <c r="C13" s="39">
         <v>140000</v>
       </c>
       <c r="D13" s="2">
         <v>0.48</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>3000</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="13">
         <v>45853</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="42">
         <f t="shared" si="1"/>
         <v>159800</v>
       </c>
       <c r="K13" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="4" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="11">
+        <v>43</v>
+      </c>
+      <c r="C14" s="39">
         <v>160000</v>
       </c>
       <c r="D14" s="2">
@@ -1182,35 +1288,35 @@
       <c r="E14" s="9">
         <v>5000</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="13">
         <v>45854</v>
       </c>
       <c r="G14" s="1">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="42">
         <f t="shared" si="1"/>
         <v>184200</v>
       </c>
       <c r="K14" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="4" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="11">
+        <v>44</v>
+      </c>
+      <c r="C15" s="39">
         <v>180000</v>
       </c>
       <c r="D15" s="2">
@@ -1219,35 +1325,35 @@
       <c r="E15" s="9">
         <v>5000</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="13">
         <v>45855</v>
       </c>
       <c r="G15" s="1">
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="42">
         <f t="shared" si="1"/>
         <v>206600</v>
       </c>
       <c r="K15" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="4" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="11">
+        <v>45</v>
+      </c>
+      <c r="C16" s="39">
         <v>200000</v>
       </c>
       <c r="D16" s="2">
@@ -1256,35 +1362,35 @@
       <c r="E16" s="9">
         <v>5000</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="13">
         <v>45856</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="42">
         <f t="shared" si="1"/>
         <v>229000</v>
       </c>
       <c r="K16" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="11">
+        <v>46</v>
+      </c>
+      <c r="C17" s="39">
         <v>70000</v>
       </c>
       <c r="D17" s="2">
@@ -1293,35 +1399,35 @@
       <c r="E17" s="9">
         <v>2000</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="13">
         <v>45857</v>
       </c>
       <c r="G17" s="1">
         <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="42">
         <f t="shared" si="1"/>
         <v>80400</v>
       </c>
       <c r="K17" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="11">
+        <v>47</v>
+      </c>
+      <c r="C18" s="39">
         <v>90000</v>
       </c>
       <c r="D18" s="2">
@@ -1330,35 +1436,35 @@
       <c r="E18" s="9">
         <v>2000</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="13">
         <v>45858</v>
       </c>
       <c r="G18" s="1">
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="42">
         <f t="shared" si="1"/>
         <v>102800</v>
       </c>
       <c r="K18" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="11">
+        <v>48</v>
+      </c>
+      <c r="C19" s="39">
         <v>110000</v>
       </c>
       <c r="D19" s="2">
@@ -1367,35 +1473,35 @@
       <c r="E19" s="9">
         <v>3000</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="13">
         <v>45859</v>
       </c>
       <c r="G19" s="1">
         <v>3</v>
       </c>
       <c r="H19" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="42">
         <f t="shared" si="1"/>
         <v>126200</v>
       </c>
       <c r="K19" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="4" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="11">
+        <v>49</v>
+      </c>
+      <c r="C20" s="39">
         <v>50000</v>
       </c>
       <c r="D20" s="2">
@@ -1404,35 +1510,35 @@
       <c r="E20" s="9">
         <v>1000</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="13">
         <v>45860</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="42">
         <f t="shared" si="1"/>
         <v>57000</v>
       </c>
       <c r="K20" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="4" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" s="11">
+        <v>50</v>
+      </c>
+      <c r="C21" s="39">
         <v>75000</v>
       </c>
       <c r="D21" s="2">
@@ -1441,187 +1547,187 @@
       <c r="E21" s="9">
         <v>1000</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="13">
         <v>45861</v>
       </c>
       <c r="G21" s="1">
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="J21" s="9">
+      <c r="J21" s="42">
         <f t="shared" si="1"/>
         <v>85000</v>
       </c>
       <c r="K21" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="7"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="3"/>
+      <c r="C23" s="40"/>
       <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="7"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="3"/>
+      <c r="C24" s="40"/>
       <c r="E24" s="3"/>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="7"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="3"/>
+      <c r="C25" s="40"/>
       <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="7"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="3"/>
+      <c r="C26" s="40"/>
       <c r="E26" s="3"/>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="7"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="3"/>
+      <c r="C27" s="40"/>
       <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="7"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="3"/>
+      <c r="C28" s="40"/>
       <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="7"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="3"/>
+      <c r="C29" s="40"/>
       <c r="E29" s="3"/>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="7"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="3"/>
+      <c r="C30" s="40"/>
       <c r="E30" s="3"/>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="7"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="3"/>
+      <c r="C31" s="40"/>
       <c r="E31" s="3"/>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="7"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="3"/>
+      <c r="C32" s="40"/>
       <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="3"/>
+      <c r="C33" s="40"/>
       <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7"/>
       <c r="B34" s="9"/>
-      <c r="C34" s="3"/>
+      <c r="C34" s="40"/>
       <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="3"/>
+      <c r="C35" s="40"/>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="3"/>
+      <c r="C36" s="40"/>
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="3"/>
+      <c r="C37" s="40"/>
       <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="3"/>
+      <c r="C38" s="40"/>
       <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="3"/>
+      <c r="C39" s="40"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="3"/>
+      <c r="C40" s="40"/>
       <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="3"/>
+      <c r="C41" s="40"/>
       <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="3"/>
+      <c r="C42" s="40"/>
       <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="3"/>
+      <c r="C43" s="40"/>
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="3"/>
+      <c r="C44" s="40"/>
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="3"/>
+      <c r="C45" s="40"/>
       <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="3"/>
+      <c r="C46" s="40"/>
       <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7"/>
       <c r="B47" s="9"/>
-      <c r="C47" s="3"/>
+      <c r="C47" s="40"/>
       <c r="E47" s="3"/>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="3"/>
+      <c r="C48" s="40"/>
       <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7"/>
       <c r="B49" s="9"/>
-      <c r="C49" s="3"/>
+      <c r="C49" s="40"/>
       <c r="E49" s="3"/>
     </row>
     <row r="50" spans="1:5">
@@ -1635,12 +1741,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.08984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21" style="19" customWidth="1"/>
+    <col min="3" max="3" width="21" style="16" customWidth="1"/>
     <col min="4" max="4" width="14.81640625" style="9" customWidth="1"/>
     <col min="5" max="5" width="11.36328125" style="7" customWidth="1"/>
     <col min="8" max="9" width="15.7265625" customWidth="1"/>
@@ -1650,44 +1756,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="8" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>15</v>
+        <v>63</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>5</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="18">
         <v>45871</v>
       </c>
       <c r="D2" s="9">
@@ -1706,27 +1812,27 @@
         <f>Sheet1!E2</f>
         <v>1000</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="14">
         <f>E2+F2</f>
         <v>18666.666666666668</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="14">
         <f>E2+F2+G2</f>
         <v>19666.666666666668</v>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="14">
         <f>D2-E2</f>
         <v>33333.333333333328</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="18">
         <v>45902</v>
       </c>
       <c r="D3" s="9">
@@ -1744,27 +1850,27 @@
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="14">
         <f>E3+F3</f>
         <v>18666.666666666668</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="14">
         <f>E3+F3</f>
         <v>18666.666666666668</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="14">
         <f t="shared" ref="J3:J4" si="0">D3-E3</f>
         <v>16666.666666666661</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="18">
         <v>45932</v>
       </c>
       <c r="D4" s="7">
@@ -1782,27 +1888,27 @@
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="14">
         <f>E4+F4</f>
         <v>18666.666666666668</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="14">
         <f>E4+F4</f>
         <v>18666.666666666668</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="18">
         <v>45903</v>
       </c>
       <c r="D5" s="7">
@@ -1821,27 +1927,27 @@
         <f>Sheet1!E3</f>
         <v>2000</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="14">
         <f>E5+F5</f>
         <v>26133.333333333332</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="14">
         <f>E5+F5+G5</f>
         <v>28133.333333333332</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="14">
         <f>D5-E5</f>
         <v>46666.666666666672</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="18">
         <v>45933</v>
       </c>
       <c r="D6" s="7">
@@ -1859,27 +1965,27 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="14">
         <f t="shared" ref="H6:H7" si="1">E6+F6</f>
         <v>26133.333333333332</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="14">
         <f>H6+F6</f>
         <v>28933.333333333332</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="14">
         <f t="shared" ref="J6:J7" si="2">D6-E6</f>
         <v>23333.333333333339</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="18">
         <v>45964</v>
       </c>
       <c r="D7" s="7">
@@ -1897,27 +2003,27 @@
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="14">
         <f t="shared" si="1"/>
         <v>26133.333333333332</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="14">
         <f>H7+F7</f>
         <v>28933.333333333332</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="22">
+      <c r="A8" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="19">
         <v>1</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="18">
         <v>45873</v>
       </c>
       <c r="D8" s="7">
@@ -1936,27 +2042,27 @@
         <f>Sheet1!E4</f>
         <v>2000</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="14">
         <f>E8+F8</f>
         <v>33600</v>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="14">
         <f>E8+F8+G8</f>
         <v>35600</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="14">
         <f>D8-E8</f>
         <v>60000</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="A9" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="19">
         <v>2</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="18">
         <v>45904</v>
       </c>
       <c r="D9" s="7">
@@ -1974,27 +2080,27 @@
       <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9" s="16">
+      <c r="H9" s="14">
         <f>E9+F9</f>
         <v>33600</v>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="14">
         <f>E9+F9</f>
         <v>33600</v>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="14">
         <f>J8-E9</f>
         <v>30000</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="22">
-        <v>3</v>
-      </c>
-      <c r="C10" s="21">
+      <c r="A10" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="19">
+        <v>3</v>
+      </c>
+      <c r="C10" s="18">
         <v>45934</v>
       </c>
       <c r="D10" s="7">
@@ -2012,27 +2118,27 @@
       <c r="G10">
         <v>0</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="14">
         <f>E10+F10</f>
         <v>33600</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="14">
         <f>E10+F10</f>
         <v>33600</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="14">
         <f>J9-E10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="18">
         <v>45937</v>
       </c>
       <c r="D11" s="7">
@@ -2050,27 +2156,27 @@
         <f>Sheet1!E5</f>
         <v>3000</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="14">
         <f>E11+F11</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="14">
         <f>E11+F11+G11</f>
         <v>44066.666666666664</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="14">
         <f>D11-E11</f>
         <v>73333.333333333343</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="18">
         <v>45968</v>
       </c>
       <c r="D12" s="7">
@@ -2087,27 +2193,27 @@
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="14">
         <f>E12+F12</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="14">
         <f>E12+F12</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="14">
         <f>D12-E12</f>
         <v>36666.666666666679</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="18">
         <v>45998</v>
       </c>
       <c r="D13" s="9">
@@ -2124,27 +2230,27 @@
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="14">
         <f>E13+F12</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="14">
         <f>E13+F13</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="14">
         <f>D13-E13</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="18">
         <v>45969</v>
       </c>
       <c r="D14" s="9">
@@ -2163,27 +2269,27 @@
         <f>Sheet1!E6</f>
         <v>3000</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="14">
         <f>E14+F14</f>
         <v>48533.333333333336</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="14">
         <f>E14+F14+G14</f>
         <v>51533.333333333336</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="14">
         <f>D14-E14</f>
         <v>86666.666666666657</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="18">
         <v>45999</v>
       </c>
       <c r="D15" s="9">
@@ -2201,27 +2307,27 @@
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="14">
         <f>E15+F15</f>
         <v>48533.333333333336</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="14">
         <f>E15+F15</f>
         <v>48533.333333333336</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="14">
         <f>D15-E15</f>
         <v>43333.333333333321</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="18">
         <v>46030</v>
       </c>
       <c r="D16" s="9">
@@ -2239,529 +2345,892 @@
       <c r="G16">
         <v>0</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="14">
         <f>E16+F16</f>
         <v>48533.333333333336</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="14">
         <f>E16+F16</f>
         <v>48533.333333333336</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="14">
         <f>D16-E16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="17" spans="1:11">
+      <c r="A17" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="20">
         <v>1</v>
       </c>
       <c r="C17" s="21">
         <v>45878</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1">
+      <c r="D17" s="22">
+        <f>Sheet1!C7</f>
+        <v>150000</v>
+      </c>
+      <c r="E17" s="23">
+        <f>Sheet1!C7/Sheet1!G7</f>
+        <v>25000</v>
+      </c>
+      <c r="F17" s="24">
+        <f>Sheet1!C7*Sheet1!I7</f>
+        <v>6000</v>
+      </c>
+      <c r="G17" s="24">
+        <f>Sheet1!E7</f>
+        <v>5000</v>
+      </c>
+      <c r="H17" s="25">
+        <f>D17/Sheet1!G7</f>
+        <v>25000</v>
+      </c>
+      <c r="I17" s="25">
+        <f>E17+G17+F17</f>
+        <v>36000</v>
+      </c>
+      <c r="J17" s="25">
+        <f>D17-E17</f>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="20">
         <v>2</v>
       </c>
       <c r="C18" s="21">
         <v>45909</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1">
+      <c r="D18" s="22">
+        <f>J17</f>
+        <v>125000</v>
+      </c>
+      <c r="E18" s="23">
+        <f>E17</f>
+        <v>25000</v>
+      </c>
+      <c r="F18" s="24">
+        <f>F17</f>
+        <v>6000</v>
+      </c>
+      <c r="G18" s="24">
+        <v>0</v>
+      </c>
+      <c r="H18" s="25">
+        <f>H17</f>
+        <v>25000</v>
+      </c>
+      <c r="I18" s="25">
+        <f>E18+F18</f>
+        <v>31000</v>
+      </c>
+      <c r="J18" s="25">
+        <f>D18-H18</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="20">
         <v>3</v>
       </c>
       <c r="C19" s="21">
         <v>45939</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1">
+      <c r="D19" s="22">
+        <f>D18-H18</f>
+        <v>100000</v>
+      </c>
+      <c r="E19" s="23">
+        <f t="shared" ref="E19:E22" si="3">E18</f>
+        <v>25000</v>
+      </c>
+      <c r="F19" s="24">
+        <f t="shared" ref="F19:F22" si="4">F18</f>
+        <v>6000</v>
+      </c>
+      <c r="G19" s="24">
+        <v>0</v>
+      </c>
+      <c r="H19" s="25">
+        <f t="shared" ref="H19:H22" si="5">H18</f>
+        <v>25000</v>
+      </c>
+      <c r="I19" s="25">
+        <f t="shared" ref="I19:I26" si="6">E19+F19</f>
+        <v>31000</v>
+      </c>
+      <c r="J19" s="25">
+        <f t="shared" ref="J19:J26" si="7">D19-H19</f>
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="20">
+        <v>4</v>
+      </c>
+      <c r="C20" s="21">
+        <v>45970</v>
+      </c>
+      <c r="D20" s="22">
+        <f t="shared" ref="D20:D23" si="8">D19-H19</f>
+        <v>75000</v>
+      </c>
+      <c r="E20" s="23">
+        <f t="shared" si="3"/>
+        <v>25000</v>
+      </c>
+      <c r="F20" s="24">
+        <f t="shared" si="4"/>
+        <v>6000</v>
+      </c>
+      <c r="G20" s="24">
+        <v>0</v>
+      </c>
+      <c r="H20" s="25">
+        <f t="shared" si="5"/>
+        <v>25000</v>
+      </c>
+      <c r="I20" s="25">
+        <f t="shared" si="6"/>
+        <v>31000</v>
+      </c>
+      <c r="J20" s="25">
+        <f t="shared" si="7"/>
+        <v>50000</v>
+      </c>
+      <c r="K20" s="14">
+        <f>SUM(I17:I22)</f>
+        <v>191000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="20">
+        <v>5</v>
+      </c>
+      <c r="C21" s="21">
+        <v>46000</v>
+      </c>
+      <c r="D21" s="22">
+        <f t="shared" si="8"/>
+        <v>50000</v>
+      </c>
+      <c r="E21" s="23">
+        <f t="shared" si="3"/>
+        <v>25000</v>
+      </c>
+      <c r="F21" s="24">
+        <f t="shared" si="4"/>
+        <v>6000</v>
+      </c>
+      <c r="G21" s="24">
+        <v>0</v>
+      </c>
+      <c r="H21" s="25">
+        <f t="shared" si="5"/>
+        <v>25000</v>
+      </c>
+      <c r="I21" s="25">
+        <f t="shared" si="6"/>
+        <v>31000</v>
+      </c>
+      <c r="J21" s="25">
+        <f t="shared" si="7"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="20">
+        <v>6</v>
+      </c>
+      <c r="C22" s="21">
+        <v>46031</v>
+      </c>
+      <c r="D22" s="22">
+        <f t="shared" si="8"/>
+        <v>25000</v>
+      </c>
+      <c r="E22" s="23">
+        <f t="shared" si="3"/>
+        <v>25000</v>
+      </c>
+      <c r="F22" s="24">
+        <f t="shared" si="4"/>
+        <v>6000</v>
+      </c>
+      <c r="G22" s="24">
+        <v>0</v>
+      </c>
+      <c r="H22" s="25">
+        <f t="shared" si="5"/>
+        <v>25000</v>
+      </c>
+      <c r="I22" s="25">
+        <f t="shared" si="6"/>
+        <v>31000</v>
+      </c>
+      <c r="J22" s="25">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="19">
         <v>1</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C23" s="26">
         <v>45879</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" s="21">
-        <v>45910</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="1">
-        <v>3</v>
-      </c>
-      <c r="C22" s="21">
-        <v>45940</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1</v>
-      </c>
-      <c r="C23" s="21">
-        <v>45880</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="27">
+        <f>Sheet1!C8</f>
+        <v>170000</v>
+      </c>
+      <c r="E23" s="28">
+        <f>Sheet1!C8/Sheet1!G8</f>
+        <v>56666.666666666664</v>
+      </c>
+      <c r="F23" s="29">
+        <f>Sheet1!C8*Sheet1!I8</f>
+        <v>6800</v>
+      </c>
+      <c r="G23" s="29">
+        <f>Sheet1!E8</f>
+        <v>2500</v>
+      </c>
+      <c r="H23" s="30">
+        <f>Sheet1!C8/Sheet1!G8</f>
+        <v>56666.666666666664</v>
+      </c>
+      <c r="I23" s="30">
+        <f>H23+F23+G23</f>
+        <v>65966.666666666657</v>
+      </c>
+      <c r="J23" s="30">
+        <f t="shared" si="7"/>
+        <v>113333.33333333334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
-      <c r="C24" s="21">
-        <v>45911</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="C24" s="18">
+        <v>45910</v>
+      </c>
+      <c r="D24" s="9">
+        <f>J23</f>
+        <v>113333.33333333334</v>
+      </c>
+      <c r="E24" s="28">
+        <f>E23</f>
+        <v>56666.666666666664</v>
+      </c>
+      <c r="F24" s="29">
+        <f>F23</f>
+        <v>6800</v>
+      </c>
+      <c r="G24" s="29">
+        <v>0</v>
+      </c>
+      <c r="H24" s="30">
+        <f>H23</f>
+        <v>56666.666666666664</v>
+      </c>
+      <c r="I24" s="30">
+        <f t="shared" si="6"/>
+        <v>63466.666666666664</v>
+      </c>
+      <c r="J24" s="30">
+        <f t="shared" si="7"/>
+        <v>56666.666666666679</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B25" s="1">
         <v>3</v>
       </c>
-      <c r="C25" s="21">
-        <v>45941</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="C25" s="18">
+        <v>45940</v>
+      </c>
+      <c r="D25" s="9">
+        <f>J24</f>
+        <v>56666.666666666679</v>
+      </c>
+      <c r="E25" s="28">
+        <f>E24</f>
+        <v>56666.666666666664</v>
+      </c>
+      <c r="F25" s="29">
+        <f>F24</f>
+        <v>6800</v>
+      </c>
+      <c r="G25" s="29">
+        <v>0</v>
+      </c>
+      <c r="H25" s="30">
+        <f>H24</f>
+        <v>56666.666666666664</v>
+      </c>
+      <c r="I25" s="30">
+        <f t="shared" si="6"/>
+        <v>63466.666666666664</v>
+      </c>
+      <c r="J25" s="30">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
       </c>
-      <c r="C26" s="21">
-        <v>45881</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="C26" s="18">
+        <v>45880</v>
+      </c>
+      <c r="D26" s="9">
+        <f>Sheet1!C9</f>
+        <v>60000</v>
+      </c>
+      <c r="E26" s="28">
+        <f>Sheet1!C9/Sheet1!G9</f>
+        <v>20000</v>
+      </c>
+      <c r="F26" s="29">
+        <f>Sheet1!C9*Sheet1!I9</f>
+        <v>2400</v>
+      </c>
+      <c r="G26" s="29">
+        <f>Sheet1!E9</f>
+        <v>1000</v>
+      </c>
+      <c r="H26" s="30">
+        <f>E26+F26</f>
+        <v>22400</v>
+      </c>
+      <c r="I26" s="30">
+        <f>F26+E26+G26</f>
+        <v>23400</v>
+      </c>
+      <c r="J26" s="30">
+        <f>D26-H26</f>
+        <v>37600</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B27" s="1">
         <v>2</v>
       </c>
-      <c r="C27" s="21">
-        <v>45912</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="C27" s="18">
+        <v>45911</v>
+      </c>
+      <c r="D27" s="9">
+        <f>J26</f>
+        <v>37600</v>
+      </c>
+      <c r="E27" s="7">
+        <f>E26</f>
+        <v>20000</v>
+      </c>
+      <c r="F27">
+        <v>2400</v>
+      </c>
+      <c r="G27" s="29">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <f>H26</f>
+        <v>22400</v>
+      </c>
+      <c r="I27" s="14">
+        <f>E27+F27</f>
+        <v>22400</v>
+      </c>
+      <c r="J27" s="14">
+        <f>D27-H27</f>
+        <v>15200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
-      <c r="C28" s="21">
-        <v>45942</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="C28" s="18">
+        <v>45941</v>
+      </c>
+      <c r="D28" s="9">
+        <f>J27</f>
+        <v>15200</v>
+      </c>
+      <c r="E28" s="7">
+        <f>E27</f>
+        <v>20000</v>
+      </c>
+      <c r="F28">
+        <v>2400</v>
+      </c>
+      <c r="G28" s="29">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <f>H27</f>
+        <v>22400</v>
+      </c>
+      <c r="I28" s="14">
+        <f>E28+F28</f>
+        <v>22400</v>
+      </c>
+      <c r="J28" s="14">
+        <f>D28-H28</f>
+        <v>-7200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
       </c>
-      <c r="C29" s="21">
-        <v>45882</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="C29" s="18">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1">
         <v>2</v>
       </c>
-      <c r="C30" s="21">
-        <v>45913</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="C30" s="18">
+        <v>45912</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
       </c>
-      <c r="C31" s="21">
-        <v>45943</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="C31" s="18">
+        <v>45942</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
       </c>
-      <c r="C32" s="21">
-        <v>45883</v>
+      <c r="C32" s="18">
+        <v>45882</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B33" s="1">
         <v>2</v>
       </c>
-      <c r="C33" s="21">
-        <v>45914</v>
+      <c r="C33" s="18">
+        <v>45913</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
       </c>
-      <c r="C34" s="21">
-        <v>45944</v>
+      <c r="C34" s="18">
+        <v>45943</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B35" s="1">
         <v>1</v>
       </c>
-      <c r="C35" s="21">
-        <v>45884</v>
+      <c r="C35" s="18">
+        <v>45883</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B36" s="1">
         <v>2</v>
       </c>
-      <c r="C36" s="21">
-        <v>45915</v>
+      <c r="C36" s="18">
+        <v>45914</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="B37" s="1">
         <v>3</v>
       </c>
-      <c r="C37" s="21">
-        <v>45945</v>
+      <c r="C37" s="18">
+        <v>45944</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B38" s="1">
         <v>1</v>
       </c>
-      <c r="C38" s="21">
-        <v>45885</v>
+      <c r="C38" s="18">
+        <v>45884</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1">
         <v>2</v>
       </c>
-      <c r="C39" s="21">
-        <v>45916</v>
+      <c r="C39" s="18">
+        <v>45915</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B40" s="1">
         <v>3</v>
       </c>
-      <c r="C40" s="21">
-        <v>45946</v>
+      <c r="C40" s="18">
+        <v>45945</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B41" s="1">
         <v>1</v>
       </c>
-      <c r="C41" s="21">
-        <v>45886</v>
+      <c r="C41" s="18">
+        <v>45885</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B42" s="1">
         <v>2</v>
       </c>
-      <c r="C42" s="21">
-        <v>45917</v>
+      <c r="C42" s="18">
+        <v>45916</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B43" s="1">
         <v>3</v>
       </c>
-      <c r="C43" s="21">
-        <v>45947</v>
+      <c r="C43" s="18">
+        <v>45946</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B44" s="1">
         <v>1</v>
       </c>
-      <c r="C44" s="21">
-        <v>45887</v>
+      <c r="C44" s="18">
+        <v>45886</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B45" s="1">
         <v>2</v>
       </c>
-      <c r="C45" s="21">
-        <v>45918</v>
+      <c r="C45" s="18">
+        <v>45917</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B46" s="1">
         <v>3</v>
       </c>
-      <c r="C46" s="21">
-        <v>45948</v>
+      <c r="C46" s="18">
+        <v>45947</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B47" s="1">
         <v>1</v>
       </c>
-      <c r="C47" s="21">
-        <v>45888</v>
+      <c r="C47" s="18">
+        <v>45887</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B48" s="1">
         <v>2</v>
       </c>
-      <c r="C48" s="21">
-        <v>45919</v>
+      <c r="C48" s="18">
+        <v>45918</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="B49" s="1">
         <v>3</v>
       </c>
-      <c r="C49" s="21">
-        <v>45949</v>
+      <c r="C49" s="18">
+        <v>45948</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B50" s="1">
         <v>1</v>
       </c>
-      <c r="C50" s="21">
-        <v>45889</v>
+      <c r="C50" s="18">
+        <v>45888</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B51" s="1">
         <v>2</v>
       </c>
-      <c r="C51" s="21">
-        <v>45920</v>
+      <c r="C51" s="18">
+        <v>45919</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1">
         <v>3</v>
       </c>
-      <c r="C52" s="21">
-        <v>45950</v>
+      <c r="C52" s="18">
+        <v>45949</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B53" s="1">
         <v>1</v>
       </c>
-      <c r="C53" s="21">
-        <v>45890</v>
+      <c r="C53" s="18">
+        <v>45889</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B54" s="1">
         <v>2</v>
       </c>
-      <c r="C54" s="21">
-        <v>45921</v>
+      <c r="C54" s="18">
+        <v>45920</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B55" s="1">
         <v>3</v>
       </c>
-      <c r="C55" s="21">
-        <v>45951</v>
+      <c r="C55" s="18">
+        <v>45950</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B56" s="1">
         <v>1</v>
       </c>
-      <c r="C56" s="21">
-        <v>45891</v>
+      <c r="C56" s="18">
+        <v>45890</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B57" s="1">
         <v>2</v>
       </c>
-      <c r="C57" s="21">
-        <v>45922</v>
+      <c r="C57" s="18">
+        <v>45921</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B58" s="1">
         <v>3</v>
       </c>
-      <c r="C58" s="21">
-        <v>45952</v>
+      <c r="C58" s="18">
+        <v>45951</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B59" s="1">
         <v>1</v>
       </c>
-      <c r="C59" s="21">
-        <v>45892</v>
+      <c r="C59" s="18">
+        <v>45891</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B60" s="1">
         <v>2</v>
       </c>
-      <c r="C60" s="21">
-        <v>45923</v>
+      <c r="C60" s="18">
+        <v>45922</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B61" s="1">
         <v>3</v>
       </c>
-      <c r="C61" s="21">
+      <c r="C61" s="18">
+        <v>45952</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="18">
+        <v>45892</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" s="1">
+        <v>2</v>
+      </c>
+      <c r="C63" s="18">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B64" s="1">
+        <v>3</v>
+      </c>
+      <c r="C64" s="18">
         <v>45953</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="1"/>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="21"/>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="21"/>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="18"/>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2779,28 +3248,28 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2810,274 +3279,177 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:M12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
+    <col min="1" max="1" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="44" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.1796875" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.1796875" customWidth="1"/>
-    <col min="8" max="8" width="11.08984375" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="44"/>
+    <col min="6" max="6" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7265625" style="15" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24.1796875" customWidth="1"/>
     <col min="13" max="13" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13">
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="14">
+    <row r="1" spans="1:13">
+      <c r="A1" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="M1"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="43">
         <v>50000</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="14">
+      <c r="C2" s="33">
+        <v>3</v>
+      </c>
+      <c r="D2" s="34">
+        <v>0.04</v>
+      </c>
+      <c r="E2" s="43">
+        <v>1000</v>
+      </c>
+      <c r="F2" s="35">
+        <f>B2+(B2*D2*C2)+E2</f>
+        <v>57000</v>
+      </c>
+      <c r="G2" s="35">
+        <f>(-PMT(D2,C2,B2))*C2+E2</f>
+        <v>55052.280881599174</v>
+      </c>
+      <c r="H2" s="36">
+        <f>F2-G2</f>
+        <v>1947.7191184008261</v>
+      </c>
+      <c r="M2"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="43">
         <v>150000</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="14">
+      <c r="C3" s="33">
+        <v>6</v>
+      </c>
+      <c r="D3" s="34">
+        <v>0.04</v>
+      </c>
+      <c r="E3" s="43">
+        <v>5000</v>
+      </c>
+      <c r="F3" s="35">
+        <f>B3+(B3*D3*C3)+E3</f>
+        <v>191000</v>
+      </c>
+      <c r="G3" s="35">
+        <f>(-PMT(D3,C3,B3))*C3+E3</f>
+        <v>176685.71225715862</v>
+      </c>
+      <c r="H3" s="36">
+        <f>F3-G3</f>
+        <v>14314.287742841378</v>
+      </c>
+      <c r="M3"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="43">
         <v>500000</v>
       </c>
-    </row>
-    <row r="2" spans="3:13">
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="12">
-        <v>0.48</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="12">
-        <v>0.48</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M2" s="12">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="3" spans="3:13">
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="14">
-        <v>1000</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="14">
-        <v>3000</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="14">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="4" spans="3:13">
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="14">
-        <v>45757</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="18">
-        <v>46148</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M4" s="14">
-        <v>46208</v>
-      </c>
-    </row>
-    <row r="5" spans="3:13">
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="3:13">
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="14">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="14">
-        <v>6</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M6" s="14">
+      <c r="C4" s="33">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="3:13">
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2">
-        <f>D2/12</f>
+      <c r="D4" s="34">
         <v>0.04</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="2">
-        <f>H2/12</f>
-        <v>0.04</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="2">
-        <f>M2/12</f>
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="8" spans="3:13">
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="9">
-        <f>D1*D7</f>
-        <v>2000</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="9">
-        <f>H1*H7</f>
-        <v>6000</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M8" s="9">
-        <f>M1*M7</f>
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="9" spans="3:13">
-      <c r="C9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="9">
-        <f>D11/D6</f>
-        <v>19000</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="9">
-        <f>H1/H6+H8</f>
-        <v>31000</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M9" s="9">
-        <f>M1/M6+M8</f>
-        <v>61666.666666666664</v>
-      </c>
-    </row>
-    <row r="10" spans="3:13">
-      <c r="C10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="9">
-        <f>D9*D6</f>
-        <v>57000</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="9">
-        <f>H9*H6</f>
-        <v>186000</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M10" s="9">
-        <f>M9*M6</f>
-        <v>740000</v>
-      </c>
-    </row>
-    <row r="11" spans="3:13">
-      <c r="C11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="9">
-        <f>D1+D3+D12</f>
-        <v>57000</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="9">
-        <f>H1+H3+H12</f>
-        <v>189000</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="9">
-        <f>M1+M3+M12</f>
-        <v>745000</v>
-      </c>
-    </row>
-    <row r="12" spans="3:13">
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="9">
-        <f>D8*D6</f>
-        <v>6000</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="9">
-        <f>H8*H6</f>
-        <v>36000</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M12" s="9">
-        <f>M8*M6</f>
-        <v>240000</v>
-      </c>
+      <c r="E4" s="46">
+        <v>12500</v>
+      </c>
+      <c r="F4" s="35">
+        <f>B4+(B4*D4*C4)+E4</f>
+        <v>752500</v>
+      </c>
+      <c r="G4" s="35">
+        <f>(-PMT(D4,C4,B4))*C4+E4</f>
+        <v>651813.0361163395</v>
+      </c>
+      <c r="H4" s="36">
+        <f>F4-G4</f>
+        <v>100686.9638836605</v>
+      </c>
+      <c r="M4"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="D5"/>
+      <c r="H5"/>
+      <c r="M5"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="D6"/>
+      <c r="H6"/>
+      <c r="M6"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="D7"/>
+      <c r="H7"/>
+      <c r="M7"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="D8"/>
+      <c r="H8"/>
+      <c r="M8"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="D9"/>
+      <c r="H9"/>
+      <c r="M9"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="D10"/>
+      <c r="H10"/>
+      <c r="M10"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="D11"/>
+      <c r="H11"/>
+      <c r="M11"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="D12"/>
+      <c r="H12"/>
+      <c r="M12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/week_2/Input Data.xlsx
+++ b/week_2/Input Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13280" windowHeight="5040" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13280" windowHeight="5040" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
@@ -269,8 +269,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="\₦#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="\₦#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -482,9 +482,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -497,12 +497,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2165,7 +2165,7 @@
         <v>44066.666666666664</v>
       </c>
       <c r="J11" s="14">
-        <f>D11-E11</f>
+        <f t="shared" ref="J11:J17" si="3">D11-E11</f>
         <v>73333.333333333343</v>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v>41066.666666666664</v>
       </c>
       <c r="J12" s="14">
-        <f>D12-E12</f>
+        <f t="shared" si="3"/>
         <v>36666.666666666679</v>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
         <v>41066.666666666664</v>
       </c>
       <c r="J13" s="14">
-        <f>D13-E13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
         <v>51533.333333333336</v>
       </c>
       <c r="J14" s="14">
-        <f>D14-E14</f>
+        <f t="shared" si="3"/>
         <v>86666.666666666657</v>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>48533.333333333336</v>
       </c>
       <c r="J15" s="14">
-        <f>D15-E15</f>
+        <f t="shared" si="3"/>
         <v>43333.333333333321</v>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
         <v>48533.333333333336</v>
       </c>
       <c r="J16" s="14">
-        <f>D16-E16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>36000</v>
       </c>
       <c r="J17" s="25">
-        <f>D17-E17</f>
+        <f t="shared" si="3"/>
         <v>125000</v>
       </c>
     </row>
@@ -2450,26 +2450,26 @@
         <v>100000</v>
       </c>
       <c r="E19" s="23">
-        <f t="shared" ref="E19:E22" si="3">E18</f>
+        <f t="shared" ref="E19:E22" si="4">E18</f>
         <v>25000</v>
       </c>
       <c r="F19" s="24">
-        <f t="shared" ref="F19:F22" si="4">F18</f>
+        <f t="shared" ref="F19:F22" si="5">F18</f>
         <v>6000</v>
       </c>
       <c r="G19" s="24">
         <v>0</v>
       </c>
       <c r="H19" s="25">
-        <f t="shared" ref="H19:H22" si="5">H18</f>
+        <f t="shared" ref="H19:H22" si="6">H18</f>
         <v>25000</v>
       </c>
       <c r="I19" s="25">
-        <f t="shared" ref="I19:I26" si="6">E19+F19</f>
+        <f t="shared" ref="I19:I25" si="7">E19+F19</f>
         <v>31000</v>
       </c>
       <c r="J19" s="25">
-        <f t="shared" ref="J19:J26" si="7">D19-H19</f>
+        <f t="shared" ref="J19:J25" si="8">D19-H19</f>
         <v>75000</v>
       </c>
     </row>
@@ -2484,30 +2484,30 @@
         <v>45970</v>
       </c>
       <c r="D20" s="22">
-        <f t="shared" ref="D20:D23" si="8">D19-H19</f>
+        <f t="shared" ref="D20:D22" si="9">D19-H19</f>
         <v>75000</v>
       </c>
       <c r="E20" s="23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25000</v>
       </c>
       <c r="F20" s="24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6000</v>
       </c>
       <c r="G20" s="24">
         <v>0</v>
       </c>
       <c r="H20" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>25000</v>
       </c>
       <c r="I20" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>31000</v>
       </c>
       <c r="J20" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>50000</v>
       </c>
       <c r="K20" s="14">
@@ -2526,30 +2526,30 @@
         <v>46000</v>
       </c>
       <c r="D21" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>50000</v>
       </c>
       <c r="E21" s="23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25000</v>
       </c>
       <c r="F21" s="24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6000</v>
       </c>
       <c r="G21" s="24">
         <v>0</v>
       </c>
       <c r="H21" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>25000</v>
       </c>
       <c r="I21" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>31000</v>
       </c>
       <c r="J21" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>25000</v>
       </c>
     </row>
@@ -2564,30 +2564,30 @@
         <v>46031</v>
       </c>
       <c r="D22" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>25000</v>
       </c>
       <c r="E22" s="23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>25000</v>
       </c>
       <c r="F22" s="24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>6000</v>
       </c>
       <c r="G22" s="24">
         <v>0</v>
       </c>
       <c r="H22" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>25000</v>
       </c>
       <c r="I22" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>31000</v>
       </c>
       <c r="J22" s="25">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
         <v>65966.666666666657</v>
       </c>
       <c r="J23" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>113333.33333333334</v>
       </c>
     </row>
@@ -2660,11 +2660,11 @@
         <v>56666.666666666664</v>
       </c>
       <c r="I24" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>63466.666666666664</v>
       </c>
       <c r="J24" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>56666.666666666679</v>
       </c>
     </row>
@@ -2698,11 +2698,11 @@
         <v>56666.666666666664</v>
       </c>
       <c r="I25" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>63466.666666666664</v>
       </c>
       <c r="J25" s="30">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -2829,6 +2829,34 @@
       <c r="C29" s="18">
         <v>45881</v>
       </c>
+      <c r="D29" s="9">
+        <f>Sheet1!C10</f>
+        <v>80000</v>
+      </c>
+      <c r="E29" s="7">
+        <f>Sheet1!C10/Sheet1!G10</f>
+        <v>26666.666666666668</v>
+      </c>
+      <c r="F29">
+        <f>Sheet1!C10*Sheet1!I10</f>
+        <v>3200</v>
+      </c>
+      <c r="G29">
+        <f>Sheet1!E9</f>
+        <v>1000</v>
+      </c>
+      <c r="H29" s="14">
+        <f>E29+F29</f>
+        <v>29866.666666666668</v>
+      </c>
+      <c r="I29" s="14">
+        <f>E29+F29+G29</f>
+        <v>30866.666666666668</v>
+      </c>
+      <c r="J29" s="14">
+        <f>D29-H29</f>
+        <v>50133.333333333328</v>
+      </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
@@ -2840,6 +2868,33 @@
       <c r="C30" s="18">
         <v>45912</v>
       </c>
+      <c r="D30" s="9">
+        <f>J29</f>
+        <v>50133.333333333328</v>
+      </c>
+      <c r="E30" s="7">
+        <f>E29</f>
+        <v>26666.666666666668</v>
+      </c>
+      <c r="F30">
+        <f>F29</f>
+        <v>3200</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <f>H29</f>
+        <v>29866.666666666668</v>
+      </c>
+      <c r="I30" s="14">
+        <f>E30+F30</f>
+        <v>29866.666666666668</v>
+      </c>
+      <c r="J30" s="14">
+        <f t="shared" ref="J30:J34" si="10">D30-H30</f>
+        <v>20266.666666666661</v>
+      </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
@@ -2851,6 +2906,33 @@
       <c r="C31" s="18">
         <v>45942</v>
       </c>
+      <c r="D31" s="9">
+        <f>D30-E30</f>
+        <v>23466.666666666661</v>
+      </c>
+      <c r="E31" s="7">
+        <f>E30</f>
+        <v>26666.666666666668</v>
+      </c>
+      <c r="F31">
+        <f>F30</f>
+        <v>3200</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <f>H30</f>
+        <v>29866.666666666668</v>
+      </c>
+      <c r="I31" s="14">
+        <f>E31+F31</f>
+        <v>29866.666666666668</v>
+      </c>
+      <c r="J31" s="14">
+        <f t="shared" si="10"/>
+        <v>-6400.0000000000073</v>
+      </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
@@ -2862,8 +2944,36 @@
       <c r="C32" s="18">
         <v>45882</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" s="9">
+        <f>Sheet1!C11</f>
+        <v>100000</v>
+      </c>
+      <c r="E32" s="7">
+        <f>Sheet1!C11/Sheet1!G11</f>
+        <v>33333.333333333336</v>
+      </c>
+      <c r="F32">
+        <f>Sheet1!C11*Sheet1!I11</f>
+        <v>4000</v>
+      </c>
+      <c r="G32">
+        <f>Sheet1!E11</f>
+        <v>3000</v>
+      </c>
+      <c r="H32" s="14">
+        <f>E32+F32</f>
+        <v>37333.333333333336</v>
+      </c>
+      <c r="I32" s="14">
+        <f>E32+F32+G32</f>
+        <v>40333.333333333336</v>
+      </c>
+      <c r="J32" s="14">
+        <f t="shared" si="10"/>
+        <v>62666.666666666664</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -2873,8 +2983,35 @@
       <c r="C33" s="18">
         <v>45913</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" s="9">
+        <f>J32</f>
+        <v>62666.666666666664</v>
+      </c>
+      <c r="E33" s="7">
+        <f>E32</f>
+        <v>33333.333333333336</v>
+      </c>
+      <c r="F33">
+        <f>F32</f>
+        <v>4000</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <f>H32</f>
+        <v>37333.333333333336</v>
+      </c>
+      <c r="I33" s="14">
+        <f>I32-G32</f>
+        <v>37333.333333333336</v>
+      </c>
+      <c r="J33" s="14">
+        <f t="shared" si="10"/>
+        <v>25333.333333333328</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -2884,8 +3021,35 @@
       <c r="C34" s="18">
         <v>45943</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" s="9">
+        <f>J33</f>
+        <v>25333.333333333328</v>
+      </c>
+      <c r="E34" s="7">
+        <f>E33</f>
+        <v>33333.333333333336</v>
+      </c>
+      <c r="F34">
+        <f>F33</f>
+        <v>4000</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <f>H33</f>
+        <v>37333.333333333336</v>
+      </c>
+      <c r="I34" s="14">
+        <f>I33</f>
+        <v>37333.333333333336</v>
+      </c>
+      <c r="J34" s="14">
+        <f t="shared" si="10"/>
+        <v>-12000.000000000007</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="1" t="s">
         <v>20</v>
       </c>
@@ -2896,7 +3060,7 @@
         <v>45883</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:10">
       <c r="A36" s="1" t="s">
         <v>20</v>
       </c>
@@ -2907,7 +3071,7 @@
         <v>45914</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:10">
       <c r="A37" s="1" t="s">
         <v>64</v>
       </c>
@@ -2918,7 +3082,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:10">
       <c r="A38" s="1" t="s">
         <v>21</v>
       </c>
@@ -2929,7 +3093,7 @@
         <v>45884</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:10">
       <c r="A39" s="1" t="s">
         <v>21</v>
       </c>
@@ -2940,7 +3104,7 @@
         <v>45915</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:10">
       <c r="A40" s="1" t="s">
         <v>21</v>
       </c>
@@ -2951,7 +3115,7 @@
         <v>45945</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:10">
       <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
@@ -2962,7 +3126,7 @@
         <v>45885</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:10">
       <c r="A42" s="1" t="s">
         <v>22</v>
       </c>
@@ -2973,7 +3137,7 @@
         <v>45916</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:10">
       <c r="A43" s="1" t="s">
         <v>22</v>
       </c>
@@ -2984,7 +3148,7 @@
         <v>45946</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:10">
       <c r="A44" s="1" t="s">
         <v>23</v>
       </c>
@@ -2995,7 +3159,7 @@
         <v>45886</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:10">
       <c r="A45" s="1" t="s">
         <v>23</v>
       </c>
@@ -3006,7 +3170,7 @@
         <v>45917</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:10">
       <c r="A46" s="1" t="s">
         <v>23</v>
       </c>
@@ -3017,7 +3181,7 @@
         <v>45947</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:10">
       <c r="A47" s="1" t="s">
         <v>24</v>
       </c>
@@ -3028,7 +3192,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:10">
       <c r="A48" s="1" t="s">
         <v>24</v>
       </c>

--- a/week_2/Input Data.xlsx
+++ b/week_2/Input Data.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13280" windowHeight="5040" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13280" windowHeight="5040" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
+    <sheet name="Loan Tracker" sheetId="6" r:id="rId1"/>
     <sheet name="Flat Rate Balance" sheetId="5" r:id="rId2"/>
     <sheet name="Reducing Balance Schedule" sheetId="3" r:id="rId3"/>
     <sheet name="Scenario Comparison" sheetId="4" r:id="rId4"/>
+    <sheet name="Interpretation" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="80">
   <si>
     <t>Principal (₦)</t>
   </si>
@@ -43,12 +44,6 @@
     <t>Monthly payment</t>
   </si>
   <si>
-    <t>Payment No</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
     <t>Opening Balance</t>
   </si>
   <si>
@@ -160,36 +155,6 @@
     <t>C010</t>
   </si>
   <si>
-    <t>C011</t>
-  </si>
-  <si>
-    <t>C012</t>
-  </si>
-  <si>
-    <t>C013</t>
-  </si>
-  <si>
-    <t>C014</t>
-  </si>
-  <si>
-    <t>C015</t>
-  </si>
-  <si>
-    <t>C016</t>
-  </si>
-  <si>
-    <t>C017</t>
-  </si>
-  <si>
-    <t>C018</t>
-  </si>
-  <si>
-    <t>C019</t>
-  </si>
-  <si>
-    <t>C020</t>
-  </si>
-  <si>
     <t>principal</t>
   </si>
   <si>
@@ -244,9 +209,6 @@
     <t>Flat: Total Repayment (₦)</t>
   </si>
   <si>
-    <t>Reducing: Total Repayment (₦)</t>
-  </si>
-  <si>
     <t>Savings with Reducing (₦)</t>
   </si>
   <si>
@@ -260,6 +222,60 @@
   </si>
   <si>
     <t>months</t>
+  </si>
+  <si>
+    <t>Reducing: Total Repayment</t>
+  </si>
+  <si>
+    <t>Flat: Monthly Instalment (₦, avg)</t>
+  </si>
+  <si>
+    <t>Reducing: Monthly Instalment (₦, EMI)</t>
+  </si>
+  <si>
+    <t>Flat: Total Interest+Fee (₦)</t>
+  </si>
+  <si>
+    <t>Reducing: Total Interest+Fee (₦)</t>
+  </si>
+  <si>
+    <t>Flat Effective Cost (% of principal)</t>
+  </si>
+  <si>
+    <t>Reducing Effective Cost (% of principal)</t>
+  </si>
+  <si>
+    <t>Interpretation — Total Amount Paid &amp; Affordability</t>
+  </si>
+  <si>
+    <t>1. How the two methods compare</t>
+  </si>
+  <si>
+    <t>Across all three scenarios, the flat-rate method costs noticeably more than reducing balance for the same nominal 48% annual (4% monthly) rate, because flat-rate interest is charged every month on the full original principal, while reducing-balance interest is charged only on the shrinking outstanding balance. The gap grows with the loan term: for the 3-month ₦50,000 loan the two methods are close, but for the 12-month ₦500,000 loan the flat-rate borrower pays substantially more in interest than the reducing-balance borrower for an identical stated rate. See the 'Savings with Reducing' column on the Scenario Comparison sheet for exact naira figures, which recalculate automatically if the rate, principal or term change.</t>
+  </si>
+  <si>
+    <t>2. Why this matters for disclosure</t>
+  </si>
+  <si>
+    <t>A flat 4%-per-month rate is NOT equivalent to a 4%-per-month reducing rate — its true (effective) cost is roughly double, because interest keeps accruing on principal already repaid. Any borrower comparing loans by headline rate alone will underestimate a flat-rate loan's real cost. The 'Effective Cost (% of principal)' columns quantify this: they show total interest-plus-fees as a percentage of the amount borrowed for each method, making the two directly comparable regardless of term.</t>
+  </si>
+  <si>
+    <t>3. Affordability implications</t>
+  </si>
+  <si>
+    <t>Flat-rate loans have a constant monthly instalment for the whole term (principal and interest divided evenly), which is simple to budget for but front-loads the real cost since a large share of early principal is 'wasted' paying interest that should have declined. Reducing-balance loans instead front-load a higher interest share within a level EMI that gradually shifts toward principal, so the total repayment is lower for the same rate, but the monthly amount can look less transparent to a first-time borrower. For longer tenors (the 12-month ₦500,000 scenario), the affordability gap between the two methods is largest in absolute naira terms, so the repayment method matters most precisely where borrowers are taking on the most debt.</t>
+  </si>
+  <si>
+    <t>4. Data quality</t>
+  </si>
+  <si>
+    <t>5. Bottom line</t>
+  </si>
+  <si>
+    <t>For the same headline rate, reducing balance is materially cheaper and fairer to the borrower than flat rate, with the difference widening as loan size and term increase. Lenders quoting a flat monthly rate should disclose the equivalent reducing-balance/APR figure so borrowers can assess affordability accurately; borrowers comparing offers should ask which method applies before comparing rates.</t>
+  </si>
+  <si>
+    <t>All 10 loans in the portfolio passed validation (see 'Loan Data &amp; Validation', column M): principal, fee, rate, term and disbursement date are all present and within sensible bounds, and every given Total Installment figure reconciles exactly with the flat-rate formula (Principal + Principal×Monthly Rate×Term + Fee). No missing or inconsistent entries were found; if new loans are appended below row 24 with bad data, the validation flag and conditional-formatting highlight will catch them automatically.</t>
   </si>
 </sst>
 </file>
@@ -272,12 +288,19 @@
     <numFmt numFmtId="165" formatCode="\₦#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,13 +333,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -334,14 +350,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="8" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
@@ -355,14 +363,28 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="10"/>
-      <color theme="0"/>
+      <sz val="14"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F4E78"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,14 +405,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -420,10 +460,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -434,18 +474,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -457,9 +494,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -477,32 +511,78 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -784,950 +864,670 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" style="35" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.36328125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" style="42" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.26953125" style="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>52</v>
+        <v>28</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" t="s">
-        <v>60</v>
+        <v>43</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" s="42" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="39">
+        <v>29</v>
+      </c>
+      <c r="C2" s="33">
         <v>50000</v>
       </c>
       <c r="D2" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E2" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>1000</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>45840</v>
       </c>
       <c r="G2" s="1">
         <v>3</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I2" s="5">
         <f>D2/12</f>
-        <v>0.04</v>
-      </c>
-      <c r="J2" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J2" s="36">
         <f>C2*I2*G2+C2+E2</f>
-        <v>57000</v>
+        <v>54750</v>
       </c>
       <c r="K2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="39">
+        <v>30</v>
+      </c>
+      <c r="C3" s="33">
         <v>70000</v>
       </c>
       <c r="D3" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E3" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E3" s="11">
         <v>2000</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>45872</v>
       </c>
       <c r="G3" s="1">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I21" si="0">D3/12</f>
-        <v>0.04</v>
-      </c>
-      <c r="J3" s="42">
-        <f t="shared" ref="J3:J21" si="1">C3*I3*G3+C3+E3</f>
-        <v>80400</v>
+        <f t="shared" ref="I3:I11" si="0">D3/12</f>
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J3" s="36">
+        <f t="shared" ref="J3:J11" si="1">C3*I3*G3+C3+E3</f>
+        <v>77250</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="39">
+        <v>31</v>
+      </c>
+      <c r="C4" s="33">
         <v>90000</v>
       </c>
       <c r="D4" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E4" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="11">
         <v>2000</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>45842</v>
       </c>
       <c r="G4" s="1">
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I4" s="5">
         <f>D4/12</f>
-        <v>0.04</v>
-      </c>
-      <c r="J4" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J4" s="36">
         <f t="shared" si="1"/>
-        <v>102800</v>
+        <v>98750</v>
       </c>
       <c r="K4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="39">
+        <v>32</v>
+      </c>
+      <c r="C5" s="33">
         <v>110000</v>
       </c>
       <c r="D5" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E5" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E5" s="11">
         <v>3000</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>45907</v>
       </c>
       <c r="G5" s="1">
         <v>3</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J5" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J5" s="36">
         <f t="shared" si="1"/>
-        <v>126200</v>
+        <v>121250</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="39">
+        <v>33</v>
+      </c>
+      <c r="C6" s="33">
         <v>130000</v>
       </c>
       <c r="D6" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E6" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="11">
         <v>3000</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>45938</v>
       </c>
       <c r="G6" s="1">
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J6" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J6" s="36">
         <f t="shared" si="1"/>
-        <v>148600</v>
+        <v>142750</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="39">
+        <v>34</v>
+      </c>
+      <c r="C7" s="33">
         <v>150000</v>
       </c>
       <c r="D7" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E7" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="11">
         <v>5000</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="12">
         <v>45847</v>
       </c>
       <c r="G7" s="1">
         <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J7" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J7" s="36">
         <f t="shared" si="1"/>
-        <v>191000</v>
+        <v>177500</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="39">
+        <v>35</v>
+      </c>
+      <c r="C8" s="33">
         <v>170000</v>
       </c>
       <c r="D8" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E8" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="11">
         <v>2500</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>45848</v>
       </c>
       <c r="G8" s="1">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J8" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J8" s="36">
         <f t="shared" si="1"/>
-        <v>192900</v>
+        <v>185250</v>
       </c>
       <c r="K8" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="39">
+        <v>36</v>
+      </c>
+      <c r="C9" s="33">
         <v>60000</v>
       </c>
       <c r="D9" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E9" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="11">
         <v>1000</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>45849</v>
       </c>
       <c r="G9" s="1">
         <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J9" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J9" s="36">
         <f t="shared" si="1"/>
-        <v>68200</v>
+        <v>65500</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="39">
+        <v>37</v>
+      </c>
+      <c r="C10" s="33">
         <v>80000</v>
       </c>
       <c r="D10" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E10" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E10" s="11">
         <v>2000</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>45850</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J10" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>91600</v>
+        <v>88000</v>
       </c>
       <c r="K10" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="39">
-        <v>100000</v>
+        <v>38</v>
+      </c>
+      <c r="C11" s="33">
+        <v>500000</v>
       </c>
       <c r="D11" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E11" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="E11" s="11">
         <v>3000</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>45851</v>
       </c>
       <c r="G11" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J11" s="42">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="J11" s="36">
         <f t="shared" si="1"/>
-        <v>115000</v>
+        <v>653000</v>
       </c>
       <c r="K11" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="39">
-        <v>120000</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E12" s="12">
-        <v>3000</v>
-      </c>
-      <c r="F12" s="13">
-        <v>45852</v>
-      </c>
-      <c r="G12" s="1">
-        <v>12</v>
-      </c>
-      <c r="H12" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J12" s="42">
-        <f t="shared" si="1"/>
-        <v>180600</v>
-      </c>
-      <c r="K12" t="s">
-        <v>61</v>
-      </c>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="J12"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="39">
-        <v>140000</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E13" s="12">
-        <v>3000</v>
-      </c>
-      <c r="F13" s="13">
-        <v>45853</v>
-      </c>
-      <c r="G13" s="1">
-        <v>3</v>
-      </c>
-      <c r="H13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J13" s="42">
-        <f t="shared" si="1"/>
-        <v>159800</v>
-      </c>
-      <c r="K13" t="s">
-        <v>61</v>
-      </c>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="J13"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="39">
-        <v>160000</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E14" s="9">
-        <v>5000</v>
-      </c>
-      <c r="F14" s="13">
-        <v>45854</v>
-      </c>
-      <c r="G14" s="1">
-        <v>3</v>
-      </c>
-      <c r="H14" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J14" s="42">
-        <f t="shared" si="1"/>
-        <v>184200</v>
-      </c>
-      <c r="K14" t="s">
-        <v>61</v>
-      </c>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="J14"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="39">
-        <v>180000</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E15" s="9">
-        <v>5000</v>
-      </c>
-      <c r="F15" s="13">
-        <v>45855</v>
-      </c>
-      <c r="G15" s="1">
-        <v>3</v>
-      </c>
-      <c r="H15" t="s">
-        <v>57</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J15" s="42">
-        <f t="shared" si="1"/>
-        <v>206600</v>
-      </c>
-      <c r="K15" t="s">
-        <v>61</v>
-      </c>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="J15"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="39">
-        <v>200000</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E16" s="9">
-        <v>5000</v>
-      </c>
-      <c r="F16" s="13">
-        <v>45856</v>
-      </c>
-      <c r="G16" s="1">
-        <v>3</v>
-      </c>
-      <c r="H16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J16" s="42">
-        <f t="shared" si="1"/>
-        <v>229000</v>
-      </c>
-      <c r="K16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="39">
-        <v>70000</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E17" s="9">
-        <v>2000</v>
-      </c>
-      <c r="F17" s="13">
-        <v>45857</v>
-      </c>
-      <c r="G17" s="1">
-        <v>3</v>
-      </c>
-      <c r="H17" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J17" s="42">
-        <f t="shared" si="1"/>
-        <v>80400</v>
-      </c>
-      <c r="K17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="39">
-        <v>90000</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E18" s="9">
-        <v>2000</v>
-      </c>
-      <c r="F18" s="13">
-        <v>45858</v>
-      </c>
-      <c r="G18" s="1">
-        <v>3</v>
-      </c>
-      <c r="H18" t="s">
-        <v>57</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J18" s="42">
-        <f t="shared" si="1"/>
-        <v>102800</v>
-      </c>
-      <c r="K18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="39">
-        <v>110000</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E19" s="9">
-        <v>3000</v>
-      </c>
-      <c r="F19" s="13">
-        <v>45859</v>
-      </c>
-      <c r="G19" s="1">
-        <v>3</v>
-      </c>
-      <c r="H19" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J19" s="42">
-        <f t="shared" si="1"/>
-        <v>126200</v>
-      </c>
-      <c r="K19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="39">
-        <v>50000</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F20" s="13">
-        <v>45860</v>
-      </c>
-      <c r="G20" s="1">
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>57</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J20" s="42">
-        <f t="shared" si="1"/>
-        <v>57000</v>
-      </c>
-      <c r="K20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="39">
-        <v>75000</v>
-      </c>
-      <c r="D21" s="2">
-        <v>0.48</v>
-      </c>
-      <c r="E21" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F21" s="13">
-        <v>45861</v>
-      </c>
-      <c r="G21" s="1">
-        <v>3</v>
-      </c>
-      <c r="H21" t="s">
-        <v>57</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.04</v>
-      </c>
-      <c r="J21" s="42">
-        <f t="shared" si="1"/>
-        <v>85000</v>
-      </c>
-      <c r="K21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="J21"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="7"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="40"/>
+      <c r="C23" s="34"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10">
       <c r="A24" s="7"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="40"/>
+      <c r="C24" s="34"/>
       <c r="E24" s="3"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10">
       <c r="A25" s="7"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="40"/>
+      <c r="C25" s="34"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10">
       <c r="A26" s="7"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="40"/>
+      <c r="C26" s="34"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10">
       <c r="A27" s="7"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="40"/>
+      <c r="C27" s="34"/>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10">
       <c r="A28" s="7"/>
       <c r="B28" s="9"/>
-      <c r="C28" s="40"/>
+      <c r="C28" s="34"/>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10">
       <c r="A29" s="7"/>
       <c r="B29" s="9"/>
-      <c r="C29" s="40"/>
+      <c r="C29" s="34"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10">
       <c r="A30" s="7"/>
       <c r="B30" s="9"/>
-      <c r="C30" s="40"/>
+      <c r="C30" s="34"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10">
       <c r="A31" s="7"/>
       <c r="B31" s="9"/>
-      <c r="C31" s="40"/>
+      <c r="C31" s="34"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:10">
       <c r="A32" s="7"/>
       <c r="B32" s="9"/>
-      <c r="C32" s="40"/>
+      <c r="C32" s="34"/>
       <c r="E32" s="3"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="7"/>
       <c r="B33" s="9"/>
-      <c r="C33" s="40"/>
+      <c r="C33" s="34"/>
       <c r="E33" s="3"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="7"/>
       <c r="B34" s="9"/>
-      <c r="C34" s="40"/>
+      <c r="C34" s="34"/>
       <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="7"/>
       <c r="B35" s="9"/>
-      <c r="C35" s="40"/>
+      <c r="C35" s="34"/>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="7"/>
       <c r="B36" s="9"/>
-      <c r="C36" s="40"/>
+      <c r="C36" s="34"/>
       <c r="E36" s="3"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="7"/>
       <c r="B37" s="9"/>
-      <c r="C37" s="40"/>
+      <c r="C37" s="34"/>
       <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="7"/>
       <c r="B38" s="9"/>
-      <c r="C38" s="40"/>
+      <c r="C38" s="34"/>
       <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="7"/>
       <c r="B39" s="9"/>
-      <c r="C39" s="40"/>
+      <c r="C39" s="34"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="7"/>
       <c r="B40" s="9"/>
-      <c r="C40" s="40"/>
+      <c r="C40" s="34"/>
       <c r="E40" s="3"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="7"/>
       <c r="B41" s="9"/>
-      <c r="C41" s="40"/>
+      <c r="C41" s="34"/>
       <c r="E41" s="3"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="7"/>
       <c r="B42" s="9"/>
-      <c r="C42" s="40"/>
+      <c r="C42" s="34"/>
       <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="7"/>
       <c r="B43" s="9"/>
-      <c r="C43" s="40"/>
+      <c r="C43" s="34"/>
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="7"/>
       <c r="B44" s="9"/>
-      <c r="C44" s="40"/>
+      <c r="C44" s="34"/>
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="7"/>
       <c r="B45" s="9"/>
-      <c r="C45" s="40"/>
+      <c r="C45" s="34"/>
       <c r="E45" s="3"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="7"/>
       <c r="B46" s="9"/>
-      <c r="C46" s="40"/>
+      <c r="C46" s="34"/>
       <c r="E46" s="3"/>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="7"/>
       <c r="B47" s="9"/>
-      <c r="C47" s="40"/>
+      <c r="C47" s="34"/>
       <c r="E47" s="3"/>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="7"/>
       <c r="B48" s="9"/>
-      <c r="C48" s="40"/>
+      <c r="C48" s="34"/>
       <c r="E48" s="3"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="7"/>
       <c r="B49" s="9"/>
-      <c r="C49" s="40"/>
+      <c r="C49" s="34"/>
       <c r="E49" s="3"/>
     </row>
     <row r="50" spans="1:5">
@@ -1741,12 +1541,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9" style="3" customWidth="1"/>
     <col min="2" max="2" width="9.08984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21" style="16" customWidth="1"/>
+    <col min="3" max="3" width="21" style="15" customWidth="1"/>
     <col min="4" max="4" width="14.81640625" style="9" customWidth="1"/>
     <col min="5" max="5" width="11.36328125" style="7" customWidth="1"/>
     <col min="8" max="9" width="15.7265625" customWidth="1"/>
@@ -1755,199 +1555,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="12" t="s">
+      <c r="A1" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="56">
         <v>1</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="18">
+      <c r="C2" s="57">
         <v>45871</v>
       </c>
-      <c r="D2" s="9">
-        <f>Sheet1!C2</f>
+      <c r="D2" s="58">
+        <f>'Loan Tracker'!C2</f>
         <v>50000</v>
       </c>
-      <c r="E2" s="7">
-        <f>Sheet1!C2/Sheet1!G2</f>
+      <c r="E2" s="59">
+        <f>'Loan Tracker'!C2/'Loan Tracker'!G2</f>
         <v>16666.666666666668</v>
       </c>
-      <c r="F2">
-        <f>Sheet1!C2*Sheet1!I2</f>
-        <v>2000</v>
-      </c>
-      <c r="G2">
-        <f>Sheet1!E2</f>
+      <c r="F2" s="60">
+        <f>'Loan Tracker'!C2*'Loan Tracker'!I2</f>
+        <v>1250</v>
+      </c>
+      <c r="G2" s="60">
+        <f>'Loan Tracker'!E2</f>
         <v>1000</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="61">
         <f>E2+F2</f>
-        <v>18666.666666666668</v>
-      </c>
-      <c r="I2" s="14">
+        <v>17916.666666666668</v>
+      </c>
+      <c r="I2" s="61">
         <f>E2+F2+G2</f>
-        <v>19666.666666666668</v>
-      </c>
-      <c r="J2" s="14">
+        <v>18916.666666666668</v>
+      </c>
+      <c r="J2" s="61">
         <f>D2-E2</f>
         <v>33333.333333333328</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="A3" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="56">
         <v>2</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="57">
         <v>45902</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="58">
         <f>J2</f>
         <v>33333.333333333328</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="59">
         <f>E2</f>
         <v>16666.666666666668</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="60">
         <f>F2</f>
-        <v>2000</v>
-      </c>
-      <c r="G3">
+        <v>1250</v>
+      </c>
+      <c r="G3" s="60">
         <v>0</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="61">
         <f>E3+F3</f>
-        <v>18666.666666666668</v>
-      </c>
-      <c r="I3" s="14">
+        <v>17916.666666666668</v>
+      </c>
+      <c r="I3" s="61">
         <f>E3+F3</f>
-        <v>18666.666666666668</v>
-      </c>
-      <c r="J3" s="14">
+        <v>17916.666666666668</v>
+      </c>
+      <c r="J3" s="61">
         <f t="shared" ref="J3:J4" si="0">D3-E3</f>
         <v>16666.666666666661</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="A4" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="56">
         <v>3</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="57">
         <v>45932</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="59">
         <f>D3-E3</f>
         <v>16666.666666666661</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="59">
         <f>E2</f>
         <v>16666.666666666668</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="60">
         <f>F2</f>
-        <v>2000</v>
-      </c>
-      <c r="G4">
+        <v>1250</v>
+      </c>
+      <c r="G4" s="60">
         <v>0</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="61">
         <f>E4+F4</f>
-        <v>18666.666666666668</v>
-      </c>
-      <c r="I4" s="14">
+        <v>17916.666666666668</v>
+      </c>
+      <c r="I4" s="61">
         <f>E4+F4</f>
-        <v>18666.666666666668</v>
-      </c>
-      <c r="J4" s="14">
+        <v>17916.666666666668</v>
+      </c>
+      <c r="J4" s="61">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="16">
         <v>45903</v>
       </c>
       <c r="D5" s="7">
-        <f>Sheet1!C3</f>
+        <f>'Loan Tracker'!C3</f>
         <v>70000</v>
       </c>
       <c r="E5" s="7">
-        <f>Sheet1!C3/Sheet1!G3</f>
+        <f>'Loan Tracker'!C3/'Loan Tracker'!G3</f>
         <v>23333.333333333332</v>
       </c>
       <c r="F5">
-        <f>Sheet1!C3*Sheet1!I3</f>
-        <v>2800</v>
+        <f>'Loan Tracker'!C3*'Loan Tracker'!I3</f>
+        <v>1749.9999999999998</v>
       </c>
       <c r="G5">
-        <f>Sheet1!E3</f>
+        <f>'Loan Tracker'!E3</f>
         <v>2000</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <f>E5+F5</f>
-        <v>26133.333333333332</v>
-      </c>
-      <c r="I5" s="14">
+        <v>25083.333333333332</v>
+      </c>
+      <c r="I5" s="13">
         <f>E5+F5+G5</f>
-        <v>28133.333333333332</v>
-      </c>
-      <c r="J5" s="14">
+        <v>27083.333333333332</v>
+      </c>
+      <c r="J5" s="13">
         <f>D5-E5</f>
         <v>46666.666666666672</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="16">
         <v>45933</v>
       </c>
       <c r="D6" s="7">
@@ -1960,32 +1760,32 @@
       </c>
       <c r="F6">
         <f>F5</f>
-        <v>2800</v>
+        <v>1749.9999999999998</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <f t="shared" ref="H6:H7" si="1">E6+F6</f>
-        <v>26133.333333333332</v>
-      </c>
-      <c r="I6" s="14">
+        <v>25083.333333333332</v>
+      </c>
+      <c r="I6" s="13">
         <f>H6+F6</f>
-        <v>28933.333333333332</v>
-      </c>
-      <c r="J6" s="14">
+        <v>26833.333333333332</v>
+      </c>
+      <c r="J6" s="13">
         <f t="shared" ref="J6:J7" si="2">D6-E6</f>
         <v>23333.333333333339</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="16">
         <v>45964</v>
       </c>
       <c r="D7" s="7">
@@ -1998,71 +1798,71 @@
       </c>
       <c r="F7">
         <f>F6</f>
-        <v>2800</v>
+        <v>1749.9999999999998</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <f t="shared" si="1"/>
-        <v>26133.333333333332</v>
-      </c>
-      <c r="I7" s="14">
+        <v>25083.333333333332</v>
+      </c>
+      <c r="I7" s="13">
         <f>H7+F7</f>
-        <v>28933.333333333332</v>
-      </c>
-      <c r="J7" s="14">
+        <v>26833.333333333332</v>
+      </c>
+      <c r="J7" s="13">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="19">
+      <c r="A8" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="17">
         <v>1</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="16">
         <v>45873</v>
       </c>
       <c r="D8" s="7">
-        <f>Sheet1!C4</f>
+        <f>'Loan Tracker'!C4</f>
         <v>90000</v>
       </c>
       <c r="E8" s="7">
-        <f>Sheet1!C4/Sheet1!G4</f>
+        <f>'Loan Tracker'!C4/'Loan Tracker'!G4</f>
         <v>30000</v>
       </c>
       <c r="F8">
-        <f>Sheet1!C4*Sheet1!I4</f>
-        <v>3600</v>
+        <f>'Loan Tracker'!C4*'Loan Tracker'!I4</f>
+        <v>2250</v>
       </c>
       <c r="G8">
-        <f>Sheet1!E4</f>
+        <f>'Loan Tracker'!E4</f>
         <v>2000</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <f>E8+F8</f>
-        <v>33600</v>
-      </c>
-      <c r="I8" s="14">
+        <v>32250</v>
+      </c>
+      <c r="I8" s="13">
         <f>E8+F8+G8</f>
-        <v>35600</v>
-      </c>
-      <c r="J8" s="14">
+        <v>34250</v>
+      </c>
+      <c r="J8" s="13">
         <f>D8-E8</f>
         <v>60000</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="19">
+      <c r="A9" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="17">
         <v>2</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="16">
         <v>45904</v>
       </c>
       <c r="D9" s="7">
@@ -2075,32 +1875,32 @@
       </c>
       <c r="F9">
         <f>F8</f>
-        <v>3600</v>
+        <v>2250</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <f>E9+F9</f>
-        <v>33600</v>
-      </c>
-      <c r="I9" s="14">
+        <v>32250</v>
+      </c>
+      <c r="I9" s="13">
         <f>E9+F9</f>
-        <v>33600</v>
-      </c>
-      <c r="J9" s="14">
+        <v>32250</v>
+      </c>
+      <c r="J9" s="13">
         <f>J8-E9</f>
         <v>30000</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="19">
+      <c r="A10" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="17">
         <v>3</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="16">
         <v>45934</v>
       </c>
       <c r="D10" s="7">
@@ -2113,70 +1913,70 @@
       </c>
       <c r="F10">
         <f>F9</f>
-        <v>3600</v>
+        <v>2250</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <f>E10+F10</f>
-        <v>33600</v>
-      </c>
-      <c r="I10" s="14">
+        <v>32250</v>
+      </c>
+      <c r="I10" s="13">
         <f>E10+F10</f>
-        <v>33600</v>
-      </c>
-      <c r="J10" s="14">
+        <v>32250</v>
+      </c>
+      <c r="J10" s="13">
         <f>J9-E10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="16">
         <v>45937</v>
       </c>
       <c r="D11" s="7">
-        <f>Sheet1!C5</f>
+        <f>'Loan Tracker'!C5</f>
         <v>110000</v>
       </c>
       <c r="E11" s="7">
-        <f>Sheet1!C5/Sheet1!G4</f>
+        <f>'Loan Tracker'!C5/'Loan Tracker'!G4</f>
         <v>36666.666666666664</v>
       </c>
       <c r="F11">
         <v>4400</v>
       </c>
       <c r="G11">
-        <f>Sheet1!E5</f>
+        <f>'Loan Tracker'!E5</f>
         <v>3000</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <f>E11+F11</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <f>E11+F11+G11</f>
         <v>44066.666666666664</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="13">
         <f t="shared" ref="J11:J17" si="3">D11-E11</f>
         <v>73333.333333333343</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="16">
         <v>45968</v>
       </c>
       <c r="D12" s="7">
@@ -2193,27 +1993,27 @@
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <f>E12+F12</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <f>E12+F12</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="13">
         <f t="shared" si="3"/>
         <v>36666.666666666679</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="16">
         <v>45998</v>
       </c>
       <c r="D13" s="9">
@@ -2230,66 +2030,66 @@
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <f>E13+F12</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <f>E13+F13</f>
         <v>41066.666666666664</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="16">
         <v>45969</v>
       </c>
       <c r="D14" s="9">
-        <f>Sheet1!C6</f>
+        <f>'Loan Tracker'!C6</f>
         <v>130000</v>
       </c>
       <c r="E14" s="7">
-        <f>Sheet1!C6/Sheet1!G5</f>
+        <f>'Loan Tracker'!C6/'Loan Tracker'!G5</f>
         <v>43333.333333333336</v>
       </c>
       <c r="F14">
-        <f>Sheet1!C6*Sheet1!I6</f>
-        <v>5200</v>
+        <f>'Loan Tracker'!C6*'Loan Tracker'!I6</f>
+        <v>3249.9999999999995</v>
       </c>
       <c r="G14">
-        <f>Sheet1!E6</f>
+        <f>'Loan Tracker'!E6</f>
         <v>3000</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <f>E14+F14</f>
-        <v>48533.333333333336</v>
-      </c>
-      <c r="I14" s="14">
+        <v>46583.333333333336</v>
+      </c>
+      <c r="I14" s="13">
         <f>E14+F14+G14</f>
-        <v>51533.333333333336</v>
-      </c>
-      <c r="J14" s="14">
+        <v>49583.333333333336</v>
+      </c>
+      <c r="J14" s="13">
         <f t="shared" si="3"/>
         <v>86666.666666666657</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="16">
         <v>45999</v>
       </c>
       <c r="D15" s="9">
@@ -2302,32 +2102,32 @@
       </c>
       <c r="F15">
         <f>F14</f>
-        <v>5200</v>
+        <v>3249.9999999999995</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <f>E15+F15</f>
-        <v>48533.333333333336</v>
-      </c>
-      <c r="I15" s="14">
+        <v>46583.333333333336</v>
+      </c>
+      <c r="I15" s="13">
         <f>E15+F15</f>
-        <v>48533.333333333336</v>
-      </c>
-      <c r="J15" s="14">
+        <v>46583.333333333336</v>
+      </c>
+      <c r="J15" s="13">
         <f t="shared" si="3"/>
         <v>43333.333333333321</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1">
         <v>3</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="16">
         <v>46030</v>
       </c>
       <c r="D16" s="9">
@@ -2340,424 +2140,424 @@
       </c>
       <c r="F16">
         <f>F15</f>
-        <v>5200</v>
+        <v>3249.9999999999995</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="13">
         <f>E16+F16</f>
-        <v>48533.333333333336</v>
-      </c>
-      <c r="I16" s="14">
+        <v>46583.333333333336</v>
+      </c>
+      <c r="I16" s="13">
         <f>E16+F16</f>
-        <v>48533.333333333336</v>
-      </c>
-      <c r="J16" s="14">
+        <v>46583.333333333336</v>
+      </c>
+      <c r="J16" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="20">
+      <c r="A17" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="18">
         <v>1</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="19">
         <v>45878</v>
       </c>
-      <c r="D17" s="22">
-        <f>Sheet1!C7</f>
+      <c r="D17" s="20">
+        <f>'Loan Tracker'!C7</f>
         <v>150000</v>
       </c>
-      <c r="E17" s="23">
-        <f>Sheet1!C7/Sheet1!G7</f>
+      <c r="E17" s="21">
+        <f>'Loan Tracker'!C7/'Loan Tracker'!G7</f>
         <v>25000</v>
       </c>
-      <c r="F17" s="24">
-        <f>Sheet1!C7*Sheet1!I7</f>
-        <v>6000</v>
-      </c>
-      <c r="G17" s="24">
-        <f>Sheet1!E7</f>
+      <c r="F17" s="22">
+        <f>'Loan Tracker'!C7*'Loan Tracker'!I7</f>
+        <v>3749.9999999999995</v>
+      </c>
+      <c r="G17" s="22">
+        <f>'Loan Tracker'!E7</f>
         <v>5000</v>
       </c>
-      <c r="H17" s="25">
-        <f>D17/Sheet1!G7</f>
+      <c r="H17" s="23">
+        <f>D17/'Loan Tracker'!G7</f>
         <v>25000</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="23">
         <f>E17+G17+F17</f>
-        <v>36000</v>
-      </c>
-      <c r="J17" s="25">
+        <v>33750</v>
+      </c>
+      <c r="J17" s="23">
         <f t="shared" si="3"/>
         <v>125000</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="20">
+      <c r="A18" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="18">
         <v>2</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="19">
         <v>45909</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <f>J17</f>
         <v>125000</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="21">
         <f>E17</f>
         <v>25000</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="22">
         <f>F17</f>
-        <v>6000</v>
-      </c>
-      <c r="G18" s="24">
+        <v>3749.9999999999995</v>
+      </c>
+      <c r="G18" s="22">
         <v>0</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="23">
         <f>H17</f>
         <v>25000</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="23">
         <f>E18+F18</f>
-        <v>31000</v>
-      </c>
-      <c r="J18" s="25">
+        <v>28750</v>
+      </c>
+      <c r="J18" s="23">
         <f>D18-H18</f>
         <v>100000</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="20">
+      <c r="A19" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="18">
         <v>3</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="19">
         <v>45939</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="20">
         <f>D18-H18</f>
         <v>100000</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="21">
         <f t="shared" ref="E19:E22" si="4">E18</f>
         <v>25000</v>
       </c>
-      <c r="F19" s="24">
+      <c r="F19" s="22">
         <f t="shared" ref="F19:F22" si="5">F18</f>
-        <v>6000</v>
-      </c>
-      <c r="G19" s="24">
+        <v>3749.9999999999995</v>
+      </c>
+      <c r="G19" s="22">
         <v>0</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="23">
         <f t="shared" ref="H19:H22" si="6">H18</f>
         <v>25000</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="23">
         <f t="shared" ref="I19:I25" si="7">E19+F19</f>
-        <v>31000</v>
-      </c>
-      <c r="J19" s="25">
+        <v>28750</v>
+      </c>
+      <c r="J19" s="23">
         <f t="shared" ref="J19:J25" si="8">D19-H19</f>
         <v>75000</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="20">
+      <c r="A20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="18">
         <v>4</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="19">
         <v>45970</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="20">
         <f t="shared" ref="D20:D22" si="9">D19-H19</f>
         <v>75000</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="21">
         <f t="shared" si="4"/>
         <v>25000</v>
       </c>
-      <c r="F20" s="24">
+      <c r="F20" s="22">
         <f t="shared" si="5"/>
-        <v>6000</v>
-      </c>
-      <c r="G20" s="24">
+        <v>3749.9999999999995</v>
+      </c>
+      <c r="G20" s="22">
         <v>0</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="23">
         <f t="shared" si="6"/>
         <v>25000</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="23">
         <f t="shared" si="7"/>
-        <v>31000</v>
-      </c>
-      <c r="J20" s="25">
+        <v>28750</v>
+      </c>
+      <c r="J20" s="23">
         <f t="shared" si="8"/>
         <v>50000</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <f>SUM(I17:I22)</f>
-        <v>191000</v>
+        <v>177500</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="20">
+      <c r="A21" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="18">
         <v>5</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="19">
         <v>46000</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="20">
         <f t="shared" si="9"/>
         <v>50000</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="21">
         <f t="shared" si="4"/>
         <v>25000</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="22">
         <f t="shared" si="5"/>
-        <v>6000</v>
-      </c>
-      <c r="G21" s="24">
+        <v>3749.9999999999995</v>
+      </c>
+      <c r="G21" s="22">
         <v>0</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="23">
         <f t="shared" si="6"/>
         <v>25000</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="23">
         <f t="shared" si="7"/>
-        <v>31000</v>
-      </c>
-      <c r="J21" s="25">
+        <v>28750</v>
+      </c>
+      <c r="J21" s="23">
         <f t="shared" si="8"/>
         <v>25000</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="20">
+      <c r="A22" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="18">
         <v>6</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="19">
         <v>46031</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="20">
         <f t="shared" si="9"/>
         <v>25000</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="21">
         <f t="shared" si="4"/>
         <v>25000</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F22" s="22">
         <f t="shared" si="5"/>
-        <v>6000</v>
-      </c>
-      <c r="G22" s="24">
+        <v>3749.9999999999995</v>
+      </c>
+      <c r="G22" s="22">
         <v>0</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="23">
         <f t="shared" si="6"/>
         <v>25000</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="23">
         <f t="shared" si="7"/>
-        <v>31000</v>
-      </c>
-      <c r="J22" s="25">
+        <v>28750</v>
+      </c>
+      <c r="J22" s="23">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="19">
+      <c r="A23" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="17">
         <v>1</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="24">
         <v>45879</v>
       </c>
-      <c r="D23" s="27">
-        <f>Sheet1!C8</f>
+      <c r="D23" s="25">
+        <f>'Loan Tracker'!C8</f>
         <v>170000</v>
       </c>
-      <c r="E23" s="28">
-        <f>Sheet1!C8/Sheet1!G8</f>
+      <c r="E23" s="26">
+        <f>'Loan Tracker'!C8/'Loan Tracker'!G8</f>
         <v>56666.666666666664</v>
       </c>
-      <c r="F23" s="29">
-        <f>Sheet1!C8*Sheet1!I8</f>
-        <v>6800</v>
-      </c>
-      <c r="G23" s="29">
-        <f>Sheet1!E8</f>
+      <c r="F23" s="27">
+        <f>'Loan Tracker'!C8*'Loan Tracker'!I8</f>
+        <v>4250</v>
+      </c>
+      <c r="G23" s="27">
+        <f>'Loan Tracker'!E8</f>
         <v>2500</v>
       </c>
-      <c r="H23" s="30">
-        <f>Sheet1!C8/Sheet1!G8</f>
+      <c r="H23" s="28">
+        <f>'Loan Tracker'!C8/'Loan Tracker'!G8</f>
         <v>56666.666666666664</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="28">
         <f>H23+F23+G23</f>
-        <v>65966.666666666657</v>
-      </c>
-      <c r="J23" s="30">
+        <v>63416.666666666664</v>
+      </c>
+      <c r="J23" s="28">
         <f t="shared" si="8"/>
         <v>113333.33333333334</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B24" s="1">
         <v>2</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="16">
         <v>45910</v>
       </c>
       <c r="D24" s="9">
         <f>J23</f>
         <v>113333.33333333334</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="26">
         <f>E23</f>
         <v>56666.666666666664</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="27">
         <f>F23</f>
-        <v>6800</v>
-      </c>
-      <c r="G24" s="29">
+        <v>4250</v>
+      </c>
+      <c r="G24" s="27">
         <v>0</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="28">
         <f>H23</f>
         <v>56666.666666666664</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="28">
         <f t="shared" si="7"/>
-        <v>63466.666666666664</v>
-      </c>
-      <c r="J24" s="30">
+        <v>60916.666666666664</v>
+      </c>
+      <c r="J24" s="28">
         <f t="shared" si="8"/>
         <v>56666.666666666679</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1">
         <v>3</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="16">
         <v>45940</v>
       </c>
       <c r="D25" s="9">
         <f>J24</f>
         <v>56666.666666666679</v>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="26">
         <f>E24</f>
         <v>56666.666666666664</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="27">
         <f>F24</f>
-        <v>6800</v>
-      </c>
-      <c r="G25" s="29">
+        <v>4250</v>
+      </c>
+      <c r="G25" s="27">
         <v>0</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="28">
         <f>H24</f>
         <v>56666.666666666664</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="28">
         <f t="shared" si="7"/>
-        <v>63466.666666666664</v>
-      </c>
-      <c r="J25" s="30">
+        <v>60916.666666666664</v>
+      </c>
+      <c r="J25" s="28">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1">
         <v>1</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="16">
         <v>45880</v>
       </c>
       <c r="D26" s="9">
-        <f>Sheet1!C9</f>
+        <f>'Loan Tracker'!C9</f>
         <v>60000</v>
       </c>
-      <c r="E26" s="28">
-        <f>Sheet1!C9/Sheet1!G9</f>
+      <c r="E26" s="26">
+        <f>'Loan Tracker'!C9/'Loan Tracker'!G9</f>
         <v>20000</v>
       </c>
-      <c r="F26" s="29">
-        <f>Sheet1!C9*Sheet1!I9</f>
-        <v>2400</v>
-      </c>
-      <c r="G26" s="29">
-        <f>Sheet1!E9</f>
+      <c r="F26" s="27">
+        <f>'Loan Tracker'!C9*'Loan Tracker'!I9</f>
+        <v>1499.9999999999998</v>
+      </c>
+      <c r="G26" s="27">
+        <f>'Loan Tracker'!E9</f>
         <v>1000</v>
       </c>
-      <c r="H26" s="30">
+      <c r="H26" s="28">
         <f>E26+F26</f>
-        <v>22400</v>
-      </c>
-      <c r="I26" s="30">
+        <v>21500</v>
+      </c>
+      <c r="I26" s="28">
         <f>F26+E26+G26</f>
-        <v>23400</v>
-      </c>
-      <c r="J26" s="30">
-        <f>D26-H26</f>
-        <v>37600</v>
+        <v>22500</v>
+      </c>
+      <c r="J26" s="28">
+        <f>D26-E26</f>
+        <v>40000</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B27" s="1">
         <v>2</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="16">
         <v>45911</v>
       </c>
       <c r="D27" s="9">
         <f>J26</f>
-        <v>37600</v>
+        <v>40000</v>
       </c>
       <c r="E27" s="7">
         <f>E26</f>
@@ -2766,35 +2566,35 @@
       <c r="F27">
         <v>2400</v>
       </c>
-      <c r="G27" s="29">
+      <c r="G27" s="27">
         <v>0</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <f>H26</f>
-        <v>22400</v>
-      </c>
-      <c r="I27" s="14">
+        <v>21500</v>
+      </c>
+      <c r="I27" s="13">
         <f>E27+F27</f>
         <v>22400</v>
       </c>
-      <c r="J27" s="14">
-        <f>D27-H27</f>
-        <v>15200</v>
+      <c r="J27" s="28">
+        <f t="shared" ref="J27:J28" si="10">D27-E27</f>
+        <v>20000</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B28" s="1">
         <v>3</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="16">
         <v>45941</v>
       </c>
       <c r="D28" s="9">
         <f>J27</f>
-        <v>15200</v>
+        <v>20000</v>
       </c>
       <c r="E28" s="7">
         <f>E27</f>
@@ -2803,74 +2603,74 @@
       <c r="F28">
         <v>2400</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="27">
         <v>0</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <f>H27</f>
-        <v>22400</v>
-      </c>
-      <c r="I28" s="14">
+        <v>21500</v>
+      </c>
+      <c r="I28" s="13">
         <f>E28+F28</f>
         <v>22400</v>
       </c>
-      <c r="J28" s="14">
-        <f>D28-H28</f>
-        <v>-7200</v>
+      <c r="J28" s="28">
+        <f t="shared" si="10"/>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1">
         <v>1</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="16">
         <v>45881</v>
       </c>
       <c r="D29" s="9">
-        <f>Sheet1!C10</f>
+        <f>'Loan Tracker'!C10</f>
         <v>80000</v>
       </c>
       <c r="E29" s="7">
-        <f>Sheet1!C10/Sheet1!G10</f>
+        <f>'Loan Tracker'!C10/'Loan Tracker'!G10</f>
         <v>26666.666666666668</v>
       </c>
       <c r="F29">
-        <f>Sheet1!C10*Sheet1!I10</f>
-        <v>3200</v>
+        <f>'Loan Tracker'!C10*'Loan Tracker'!I10</f>
+        <v>1999.9999999999998</v>
       </c>
       <c r="G29">
-        <f>Sheet1!E9</f>
+        <f>'Loan Tracker'!E9</f>
         <v>1000</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="13">
         <f>E29+F29</f>
-        <v>29866.666666666668</v>
-      </c>
-      <c r="I29" s="14">
+        <v>28666.666666666668</v>
+      </c>
+      <c r="I29" s="13">
         <f>E29+F29+G29</f>
-        <v>30866.666666666668</v>
-      </c>
-      <c r="J29" s="14">
-        <f>D29-H29</f>
-        <v>50133.333333333328</v>
+        <v>29666.666666666668</v>
+      </c>
+      <c r="J29" s="13">
+        <f>D29-E29</f>
+        <v>53333.333333333328</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1">
         <v>2</v>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="16">
         <v>45912</v>
       </c>
       <c r="D30" s="9">
         <f>J29</f>
-        <v>50133.333333333328</v>
+        <v>53333.333333333328</v>
       </c>
       <c r="E30" s="7">
         <f>E29</f>
@@ -2878,37 +2678,37 @@
       </c>
       <c r="F30">
         <f>F29</f>
-        <v>3200</v>
+        <v>1999.9999999999998</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="13">
         <f>H29</f>
-        <v>29866.666666666668</v>
-      </c>
-      <c r="I30" s="14">
+        <v>28666.666666666668</v>
+      </c>
+      <c r="I30" s="13">
         <f>E30+F30</f>
-        <v>29866.666666666668</v>
-      </c>
-      <c r="J30" s="14">
-        <f t="shared" ref="J30:J34" si="10">D30-H30</f>
-        <v>20266.666666666661</v>
+        <v>28666.666666666668</v>
+      </c>
+      <c r="J30" s="13">
+        <f t="shared" ref="J30:J31" si="11">D30-E30</f>
+        <v>26666.666666666661</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B31" s="1">
         <v>3</v>
       </c>
-      <c r="C31" s="18">
+      <c r="C31" s="16">
         <v>45942</v>
       </c>
       <c r="D31" s="9">
         <f>D30-E30</f>
-        <v>23466.666666666661</v>
+        <v>26666.666666666661</v>
       </c>
       <c r="E31" s="7">
         <f>E30</f>
@@ -2916,481 +2716,480 @@
       </c>
       <c r="F31">
         <f>F30</f>
-        <v>3200</v>
+        <v>1999.9999999999998</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="13">
         <f>H30</f>
-        <v>29866.666666666668</v>
-      </c>
-      <c r="I31" s="14">
+        <v>28666.666666666668</v>
+      </c>
+      <c r="I31" s="13">
         <f>E31+F31</f>
-        <v>29866.666666666668</v>
-      </c>
-      <c r="J31" s="14">
-        <f t="shared" si="10"/>
-        <v>-6400.0000000000073</v>
+        <v>28666.666666666668</v>
+      </c>
+      <c r="J31" s="13">
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" s="1">
+      <c r="A32" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="63">
         <v>1</v>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="64">
         <v>45882</v>
       </c>
-      <c r="D32" s="9">
-        <f>Sheet1!C11</f>
-        <v>100000</v>
-      </c>
-      <c r="E32" s="7">
-        <f>Sheet1!C11/Sheet1!G11</f>
-        <v>33333.333333333336</v>
-      </c>
-      <c r="F32">
-        <f>Sheet1!C11*Sheet1!I11</f>
-        <v>4000</v>
-      </c>
-      <c r="G32">
-        <f>Sheet1!E11</f>
+      <c r="D32" s="65">
+        <f>'Loan Tracker'!C11</f>
+        <v>500000</v>
+      </c>
+      <c r="E32" s="66">
+        <f>'Loan Tracker'!C11/'Loan Tracker'!G11</f>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F32" s="67">
+        <f>'Loan Tracker'!C11*'Loan Tracker'!I11</f>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G32" s="67">
+        <f>'Loan Tracker'!E11</f>
         <v>3000</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="68">
         <f>E32+F32</f>
-        <v>37333.333333333336</v>
-      </c>
-      <c r="I32" s="14">
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I32" s="68">
         <f>E32+F32+G32</f>
-        <v>40333.333333333336</v>
-      </c>
-      <c r="J32" s="14">
-        <f t="shared" si="10"/>
-        <v>62666.666666666664</v>
+        <v>57166.666666666664</v>
+      </c>
+      <c r="J32" s="68">
+        <f>D32-E32</f>
+        <v>458333.33333333331</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="1">
+      <c r="A33" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="63">
         <v>2</v>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="64">
         <v>45913</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="65">
         <f>J32</f>
-        <v>62666.666666666664</v>
-      </c>
-      <c r="E33" s="7">
+        <v>458333.33333333331</v>
+      </c>
+      <c r="E33" s="66">
         <f>E32</f>
-        <v>33333.333333333336</v>
-      </c>
-      <c r="F33">
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F33" s="67">
         <f>F32</f>
-        <v>4000</v>
-      </c>
-      <c r="G33">
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G33" s="67">
         <v>0</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="68">
         <f>H32</f>
-        <v>37333.333333333336</v>
-      </c>
-      <c r="I33" s="14">
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I33" s="68">
         <f>I32-G32</f>
-        <v>37333.333333333336</v>
-      </c>
-      <c r="J33" s="14">
-        <f t="shared" si="10"/>
-        <v>25333.333333333328</v>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J33" s="68">
+        <f>D33-E33</f>
+        <v>416666.66666666663</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="1">
+      <c r="A34" s="63" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="63">
         <v>3</v>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="64">
         <v>45943</v>
       </c>
-      <c r="D34" s="9">
-        <f>J33</f>
-        <v>25333.333333333328</v>
-      </c>
-      <c r="E34" s="7">
+      <c r="D34" s="65">
+        <f>D33-E33</f>
+        <v>416666.66666666663</v>
+      </c>
+      <c r="E34" s="66">
         <f>E33</f>
-        <v>33333.333333333336</v>
-      </c>
-      <c r="F34">
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F34" s="67">
         <f>F33</f>
-        <v>4000</v>
-      </c>
-      <c r="G34">
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G34" s="67">
         <v>0</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="68">
         <f>H33</f>
-        <v>37333.333333333336</v>
-      </c>
-      <c r="I34" s="14">
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I34" s="68">
         <f>I33</f>
-        <v>37333.333333333336</v>
-      </c>
-      <c r="J34" s="14">
-        <f t="shared" si="10"/>
-        <v>-12000.000000000007</v>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J34" s="68">
+        <f>D34-E34</f>
+        <v>374999.99999999994</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1</v>
-      </c>
-      <c r="C35" s="18">
-        <v>45883</v>
+      <c r="A35" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="63">
+        <v>4</v>
+      </c>
+      <c r="C35" s="64">
+        <v>45974</v>
+      </c>
+      <c r="D35" s="65">
+        <f t="shared" ref="D35:D43" si="12">D34-E34</f>
+        <v>374999.99999999994</v>
+      </c>
+      <c r="E35" s="66">
+        <f t="shared" ref="E35:E43" si="13">E34</f>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F35" s="67">
+        <f t="shared" ref="F35:F43" si="14">F34</f>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G35" s="67">
+        <v>0</v>
+      </c>
+      <c r="H35" s="68">
+        <f t="shared" ref="H35:H43" si="15">H34</f>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I35" s="68">
+        <f t="shared" ref="I35:I43" si="16">I34</f>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J35" s="68">
+        <f t="shared" ref="J35:J43" si="17">D35-E35</f>
+        <v>333333.33333333326</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2</v>
-      </c>
-      <c r="C36" s="18">
-        <v>45914</v>
+      <c r="A36" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="63">
+        <v>5</v>
+      </c>
+      <c r="C36" s="64">
+        <v>46004</v>
+      </c>
+      <c r="D36" s="65">
+        <f t="shared" si="12"/>
+        <v>333333.33333333326</v>
+      </c>
+      <c r="E36" s="66">
+        <f t="shared" si="13"/>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F36" s="67">
+        <f t="shared" si="14"/>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G36" s="67">
+        <v>0</v>
+      </c>
+      <c r="H36" s="68">
+        <f t="shared" si="15"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I36" s="68">
+        <f t="shared" si="16"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J36" s="68">
+        <f t="shared" si="17"/>
+        <v>291666.66666666657</v>
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B37" s="1">
-        <v>3</v>
-      </c>
-      <c r="C37" s="18">
-        <v>45944</v>
+      <c r="A37" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="63">
+        <v>6</v>
+      </c>
+      <c r="C37" s="64">
+        <v>46035</v>
+      </c>
+      <c r="D37" s="65">
+        <f t="shared" si="12"/>
+        <v>291666.66666666657</v>
+      </c>
+      <c r="E37" s="66">
+        <f t="shared" si="13"/>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F37" s="67">
+        <f t="shared" si="14"/>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G37" s="67">
+        <v>0</v>
+      </c>
+      <c r="H37" s="68">
+        <f t="shared" si="15"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I37" s="68">
+        <f t="shared" si="16"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J37" s="68">
+        <f t="shared" si="17"/>
+        <v>249999.99999999991</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="1">
-        <v>1</v>
-      </c>
-      <c r="C38" s="18">
-        <v>45884</v>
+      <c r="A38" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="69">
+        <v>7</v>
+      </c>
+      <c r="C38" s="64">
+        <v>46066</v>
+      </c>
+      <c r="D38" s="65">
+        <f t="shared" si="12"/>
+        <v>249999.99999999991</v>
+      </c>
+      <c r="E38" s="66">
+        <f t="shared" si="13"/>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F38" s="67">
+        <f t="shared" si="14"/>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G38" s="67">
+        <v>0</v>
+      </c>
+      <c r="H38" s="68">
+        <f t="shared" si="15"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I38" s="68">
+        <f t="shared" si="16"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J38" s="68">
+        <f t="shared" si="17"/>
+        <v>208333.33333333326</v>
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" s="1">
-        <v>2</v>
-      </c>
-      <c r="C39" s="18">
-        <v>45915</v>
+      <c r="A39" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="69">
+        <v>8</v>
+      </c>
+      <c r="C39" s="64">
+        <v>46094</v>
+      </c>
+      <c r="D39" s="65">
+        <f t="shared" si="12"/>
+        <v>208333.33333333326</v>
+      </c>
+      <c r="E39" s="66">
+        <f t="shared" si="13"/>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F39" s="67">
+        <f t="shared" si="14"/>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G39" s="67">
+        <v>0</v>
+      </c>
+      <c r="H39" s="68">
+        <f t="shared" si="15"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I39" s="68">
+        <f t="shared" si="16"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J39" s="68">
+        <f t="shared" si="17"/>
+        <v>166666.6666666666</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" s="1">
-        <v>3</v>
-      </c>
-      <c r="C40" s="18">
-        <v>45945</v>
+      <c r="A40" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="69">
+        <v>9</v>
+      </c>
+      <c r="C40" s="64">
+        <v>46125</v>
+      </c>
+      <c r="D40" s="65">
+        <f t="shared" si="12"/>
+        <v>166666.6666666666</v>
+      </c>
+      <c r="E40" s="66">
+        <f t="shared" si="13"/>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F40" s="67">
+        <f t="shared" si="14"/>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G40" s="67">
+        <v>0</v>
+      </c>
+      <c r="H40" s="68">
+        <f t="shared" si="15"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I40" s="68">
+        <f t="shared" si="16"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J40" s="68">
+        <f t="shared" si="17"/>
+        <v>124999.99999999994</v>
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" s="1">
-        <v>1</v>
-      </c>
-      <c r="C41" s="18">
-        <v>45885</v>
+      <c r="A41" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="69">
+        <v>10</v>
+      </c>
+      <c r="C41" s="64">
+        <v>46155</v>
+      </c>
+      <c r="D41" s="65">
+        <f t="shared" si="12"/>
+        <v>124999.99999999994</v>
+      </c>
+      <c r="E41" s="66">
+        <f t="shared" si="13"/>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F41" s="67">
+        <f t="shared" si="14"/>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G41" s="67">
+        <v>0</v>
+      </c>
+      <c r="H41" s="68">
+        <f t="shared" si="15"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I41" s="68">
+        <f t="shared" si="16"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J41" s="68">
+        <f t="shared" si="17"/>
+        <v>83333.333333333285</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2</v>
-      </c>
-      <c r="C42" s="18">
-        <v>45916</v>
+      <c r="A42" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B42" s="69">
+        <v>11</v>
+      </c>
+      <c r="C42" s="64">
+        <v>46186</v>
+      </c>
+      <c r="D42" s="65">
+        <f t="shared" si="12"/>
+        <v>83333.333333333285</v>
+      </c>
+      <c r="E42" s="66">
+        <f t="shared" si="13"/>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F42" s="67">
+        <f t="shared" si="14"/>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G42" s="67">
+        <v>0</v>
+      </c>
+      <c r="H42" s="68">
+        <f t="shared" si="15"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I42" s="68">
+        <f t="shared" si="16"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J42" s="68">
+        <f t="shared" si="17"/>
+        <v>41666.666666666621</v>
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B43" s="1">
-        <v>3</v>
-      </c>
-      <c r="C43" s="18">
-        <v>45946</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B44" s="1">
-        <v>1</v>
-      </c>
-      <c r="C44" s="18">
-        <v>45886</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="1">
-        <v>2</v>
-      </c>
-      <c r="C45" s="18">
-        <v>45917</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B46" s="1">
-        <v>3</v>
-      </c>
-      <c r="C46" s="18">
-        <v>45947</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B47" s="1">
-        <v>1</v>
-      </c>
-      <c r="C47" s="18">
-        <v>45887</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B48" s="1">
-        <v>2</v>
-      </c>
-      <c r="C48" s="18">
-        <v>45918</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B49" s="1">
-        <v>3</v>
-      </c>
-      <c r="C49" s="18">
-        <v>45948</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B50" s="1">
-        <v>1</v>
-      </c>
-      <c r="C50" s="18">
-        <v>45888</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B51" s="1">
-        <v>2</v>
-      </c>
-      <c r="C51" s="18">
-        <v>45919</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="1">
-        <v>3</v>
-      </c>
-      <c r="C52" s="18">
-        <v>45949</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" s="1">
-        <v>1</v>
-      </c>
-      <c r="C53" s="18">
-        <v>45889</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B54" s="1">
-        <v>2</v>
-      </c>
-      <c r="C54" s="18">
-        <v>45920</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B55" s="1">
-        <v>3</v>
-      </c>
-      <c r="C55" s="18">
-        <v>45950</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B56" s="1">
-        <v>1</v>
-      </c>
-      <c r="C56" s="18">
-        <v>45890</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B57" s="1">
-        <v>2</v>
-      </c>
-      <c r="C57" s="18">
-        <v>45921</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B58" s="1">
-        <v>3</v>
-      </c>
-      <c r="C58" s="18">
-        <v>45951</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B59" s="1">
-        <v>1</v>
-      </c>
-      <c r="C59" s="18">
-        <v>45891</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B60" s="1">
-        <v>2</v>
-      </c>
-      <c r="C60" s="18">
-        <v>45922</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B61" s="1">
-        <v>3</v>
-      </c>
-      <c r="C61" s="18">
-        <v>45952</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
-      </c>
-      <c r="C62" s="18">
-        <v>45892</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
-      </c>
-      <c r="C63" s="18">
-        <v>45923</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B64" s="1">
-        <v>3</v>
-      </c>
-      <c r="C64" s="18">
-        <v>45953</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="1"/>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="18"/>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="18"/>
+      <c r="A43" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" s="69">
+        <v>12</v>
+      </c>
+      <c r="C43" s="64">
+        <v>46216</v>
+      </c>
+      <c r="D43" s="65">
+        <f t="shared" si="12"/>
+        <v>41666.666666666621</v>
+      </c>
+      <c r="E43" s="66">
+        <f t="shared" si="13"/>
+        <v>41666.666666666664</v>
+      </c>
+      <c r="F43" s="67">
+        <f t="shared" si="14"/>
+        <v>12499.999999999998</v>
+      </c>
+      <c r="G43" s="67">
+        <v>0</v>
+      </c>
+      <c r="H43" s="68">
+        <f t="shared" si="15"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="I43" s="68">
+        <f t="shared" si="16"/>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="J43" s="68">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3400,41 +3199,766 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" customWidth="1"/>
+    <col min="1" max="1" width="9" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="21" style="15" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.7265625" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" customWidth="1"/>
+    <col min="8" max="8" width="15.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7265625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="C2" s="16">
+        <v>45871</v>
+      </c>
+      <c r="D2" s="3">
+        <f>'Loan Tracker'!C2</f>
+        <v>50000</v>
+      </c>
+      <c r="F2" s="3">
+        <f>'Loan Tracker'!C2*'Loan Tracker'!I2</f>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="16">
+        <v>45902</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="16">
+        <v>45932</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16">
+        <v>45903</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="16">
+        <v>45933</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="16">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="17">
+        <v>1</v>
+      </c>
+      <c r="C8" s="16">
+        <v>45873</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="17">
+        <v>2</v>
+      </c>
+      <c r="C9" s="16">
+        <v>45904</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="17">
+        <v>3</v>
+      </c>
+      <c r="C10" s="16">
+        <v>45934</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="16">
+        <v>45937</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="16">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1">
+        <v>3</v>
+      </c>
+      <c r="C13" s="16">
+        <v>45998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="16">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="16">
+        <v>45999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3</v>
+      </c>
+      <c r="C16" s="16">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="18">
+        <v>1</v>
+      </c>
+      <c r="C17" s="19">
+        <v>45878</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="18">
+        <v>2</v>
+      </c>
+      <c r="C18" s="19">
+        <v>45909</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="18">
+        <v>3</v>
+      </c>
+      <c r="C19" s="19">
+        <v>45939</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="18">
+        <v>4</v>
+      </c>
+      <c r="C20" s="19">
+        <v>45970</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="18">
+        <v>5</v>
+      </c>
+      <c r="C21" s="19">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="18">
+        <v>6</v>
+      </c>
+      <c r="C22" s="19">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="17">
+        <v>1</v>
+      </c>
+      <c r="C23" s="24">
+        <v>45879</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="16">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="16">
+        <v>45940</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1</v>
+      </c>
+      <c r="C26" s="16">
+        <v>45880</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2</v>
+      </c>
+      <c r="C27" s="16">
+        <v>45911</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="1">
+        <v>3</v>
+      </c>
+      <c r="C28" s="16">
+        <v>45941</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="16">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2</v>
+      </c>
+      <c r="C30" s="16">
+        <v>45912</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="1">
+        <v>3</v>
+      </c>
+      <c r="C31" s="16">
+        <v>45942</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="16">
+        <v>45882</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2</v>
+      </c>
+      <c r="C33" s="16">
+        <v>45913</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="1">
+        <v>3</v>
+      </c>
+      <c r="C34" s="16">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="16">
+        <v>45883</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2</v>
+      </c>
+      <c r="C36" s="16">
+        <v>45914</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="1">
+        <v>3</v>
+      </c>
+      <c r="C37" s="16">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="16">
+        <v>45884</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" s="1">
+        <v>2</v>
+      </c>
+      <c r="C39" s="16">
+        <v>45915</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" s="1">
+        <v>3</v>
+      </c>
+      <c r="C40" s="16">
+        <v>45945</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1</v>
+      </c>
+      <c r="C41" s="16">
+        <v>45885</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2</v>
+      </c>
+      <c r="C42" s="16">
+        <v>45916</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="1">
+        <v>3</v>
+      </c>
+      <c r="C43" s="16">
+        <v>45946</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1</v>
+      </c>
+      <c r="C44" s="16">
+        <v>45886</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2</v>
+      </c>
+      <c r="C45" s="16">
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="1">
+        <v>3</v>
+      </c>
+      <c r="C46" s="16">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="16">
+        <v>45887</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="1">
+        <v>2</v>
+      </c>
+      <c r="C48" s="16">
+        <v>45918</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="1">
+        <v>3</v>
+      </c>
+      <c r="C49" s="16">
+        <v>45948</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1</v>
+      </c>
+      <c r="C50" s="16">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="1">
+        <v>2</v>
+      </c>
+      <c r="C51" s="16">
+        <v>45919</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="1">
+        <v>3</v>
+      </c>
+      <c r="C52" s="16">
+        <v>45949</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="1">
+        <v>1</v>
+      </c>
+      <c r="C53" s="16">
+        <v>45889</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2</v>
+      </c>
+      <c r="C54" s="16">
+        <v>45920</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="1">
+        <v>3</v>
+      </c>
+      <c r="C55" s="16">
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" s="1">
+        <v>1</v>
+      </c>
+      <c r="C56" s="16">
+        <v>45890</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="1">
+        <v>2</v>
+      </c>
+      <c r="C57" s="16">
+        <v>45921</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" s="1">
+        <v>3</v>
+      </c>
+      <c r="C58" s="16">
+        <v>45951</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" s="1">
+        <v>1</v>
+      </c>
+      <c r="C59" s="16">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" s="1">
+        <v>2</v>
+      </c>
+      <c r="C60" s="16">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" s="1">
+        <v>3</v>
+      </c>
+      <c r="C61" s="16">
+        <v>45952</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="16">
+        <v>45892</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B63" s="1">
+        <v>2</v>
+      </c>
+      <c r="C63" s="16">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" s="1">
+        <v>3</v>
+      </c>
+      <c r="C64" s="16">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="16"/>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3447,131 +3971,135 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="44" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.1796875" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="44"/>
+    <col min="4" max="4" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="38"/>
     <col min="6" max="6" width="23.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.7265625" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7265625" style="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24.1796875" customWidth="1"/>
     <col min="13" max="13" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="45" t="s">
+      <c r="A1" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="37" t="s">
-        <v>70</v>
+      <c r="C1" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="51" t="s">
+        <v>57</v>
       </c>
       <c r="M1"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="43">
+      <c r="A2" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="37">
         <v>50000</v>
       </c>
-      <c r="C2" s="33">
+      <c r="C2" s="30">
         <v>3</v>
       </c>
-      <c r="D2" s="34">
-        <v>0.04</v>
-      </c>
-      <c r="E2" s="43">
+      <c r="D2" s="70">
+        <f>'Loan Tracker'!I2</f>
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="E2" s="37">
         <v>1000</v>
       </c>
-      <c r="F2" s="35">
+      <c r="F2" s="31">
         <f>B2+(B2*D2*C2)+E2</f>
-        <v>57000</v>
-      </c>
-      <c r="G2" s="35">
+        <v>54750</v>
+      </c>
+      <c r="G2" s="31">
         <f>(-PMT(D2,C2,B2))*C2+E2</f>
-        <v>55052.280881599174</v>
-      </c>
-      <c r="H2" s="36">
+        <v>53520.575086364552</v>
+      </c>
+      <c r="H2" s="32">
         <f>F2-G2</f>
-        <v>1947.7191184008261</v>
+        <v>1229.4249136354483</v>
       </c>
       <c r="M2"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B3" s="43">
+      <c r="A3" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="37">
         <v>150000</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="30">
         <v>6</v>
       </c>
-      <c r="D3" s="34">
-        <v>0.04</v>
-      </c>
-      <c r="E3" s="43">
+      <c r="D3" s="70">
+        <f>'Loan Tracker'!I3</f>
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="E3" s="37">
         <v>5000</v>
       </c>
-      <c r="F3" s="35">
+      <c r="F3" s="31">
         <f>B3+(B3*D3*C3)+E3</f>
-        <v>191000</v>
-      </c>
-      <c r="G3" s="35">
+        <v>177500</v>
+      </c>
+      <c r="G3" s="31">
         <f>(-PMT(D3,C3,B3))*C3+E3</f>
-        <v>176685.71225715862</v>
-      </c>
-      <c r="H3" s="36">
+        <v>168394.97395568789</v>
+      </c>
+      <c r="H3" s="32">
         <f>F3-G3</f>
-        <v>14314.287742841378</v>
+        <v>9105.0260443121078</v>
       </c>
       <c r="M3"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="43">
+      <c r="A4" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="37">
         <v>500000</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="30">
         <v>12</v>
       </c>
-      <c r="D4" s="34">
-        <v>0.04</v>
-      </c>
-      <c r="E4" s="46">
-        <v>12500</v>
-      </c>
-      <c r="F4" s="35">
+      <c r="D4" s="70">
+        <f>'Loan Tracker'!I4</f>
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="E4" s="39">
+        <f>'Loan Tracker'!E11</f>
+        <v>3000</v>
+      </c>
+      <c r="F4" s="31">
         <f>B4+(B4*D4*C4)+E4</f>
-        <v>752500</v>
-      </c>
-      <c r="G4" s="35">
+        <v>653000</v>
+      </c>
+      <c r="G4" s="31">
         <f>(-PMT(D4,C4,B4))*C4+E4</f>
-        <v>651813.0361163395</v>
-      </c>
-      <c r="H4" s="36">
+        <v>587922.76193002763</v>
+      </c>
+      <c r="H4" s="32">
         <f>F4-G4</f>
-        <v>100686.9638836605</v>
+        <v>65077.238069972373</v>
       </c>
       <c r="M4"/>
     </row>
@@ -3585,23 +4113,121 @@
       <c r="H6"/>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13">
-      <c r="D7"/>
+    <row r="7" spans="1:13" ht="58">
+      <c r="A7" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>68</v>
+      </c>
       <c r="H7"/>
       <c r="M7"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="D8"/>
+      <c r="A8" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="31">
+        <f>F2/C2</f>
+        <v>18250</v>
+      </c>
+      <c r="C8" s="31">
+        <f>-PMT(D2,C2,B2)</f>
+        <v>17506.858362121518</v>
+      </c>
+      <c r="D8" s="31">
+        <f>F2-B2</f>
+        <v>4750</v>
+      </c>
+      <c r="E8" s="31">
+        <f>G2-B2</f>
+        <v>3520.5750863645517</v>
+      </c>
+      <c r="F8" s="52">
+        <f>D8/B2</f>
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="G8" s="52">
+        <f>E8/B2</f>
+        <v>7.0411501727291034E-2</v>
+      </c>
       <c r="H8"/>
       <c r="M8"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="D9"/>
+      <c r="A9" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="31">
+        <f>F3/C3</f>
+        <v>29583.333333333332</v>
+      </c>
+      <c r="C9" s="31">
+        <f>-PMT(D3,C3,B3)</f>
+        <v>27232.495659281318</v>
+      </c>
+      <c r="D9" s="31">
+        <f>F3-B3</f>
+        <v>27500</v>
+      </c>
+      <c r="E9" s="31">
+        <f>G3-B3</f>
+        <v>18394.973955687892</v>
+      </c>
+      <c r="F9" s="52">
+        <f>D9/B3</f>
+        <v>0.18333333333333332</v>
+      </c>
+      <c r="G9" s="52">
+        <f>E9/B3</f>
+        <v>0.12263315970458595</v>
+      </c>
       <c r="H9"/>
       <c r="M9"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="D10"/>
+      <c r="A10" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="31">
+        <f>'Flat Rate Balance'!H32</f>
+        <v>54166.666666666664</v>
+      </c>
+      <c r="C10" s="31">
+        <f>-PMT(D4,C4,B4)</f>
+        <v>48743.563494168971</v>
+      </c>
+      <c r="D10" s="31">
+        <f>F4-B4</f>
+        <v>153000</v>
+      </c>
+      <c r="E10" s="31">
+        <f>G4-B4</f>
+        <v>87922.761930027627</v>
+      </c>
+      <c r="F10" s="52">
+        <f>D10/B4</f>
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="G10" s="52">
+        <f>E10/B4</f>
+        <v>0.17584552386005525</v>
+      </c>
       <c r="H10"/>
       <c r="M10"/>
     </row>
@@ -3618,4 +4244,72 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="96.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18">
+      <c r="A1" s="53" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.5">
+      <c r="A3" s="54" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="87.5">
+      <c r="A4" s="55" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.5">
+      <c r="A6" s="54" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="62.5">
+      <c r="A7" s="55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.5">
+      <c r="A9" s="54" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="87.5">
+      <c r="A10" s="55" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.5">
+      <c r="A12" s="54" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="62.5">
+      <c r="A13" s="55" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.5">
+      <c r="A15" s="54" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="409.5">
+      <c r="A16" s="55" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/week_2/Input Data.xlsx
+++ b/week_2/Input Data.xlsx
@@ -251,15 +251,9 @@
     <t>1. How the two methods compare</t>
   </si>
   <si>
-    <t>Across all three scenarios, the flat-rate method costs noticeably more than reducing balance for the same nominal 48% annual (4% monthly) rate, because flat-rate interest is charged every month on the full original principal, while reducing-balance interest is charged only on the shrinking outstanding balance. The gap grows with the loan term: for the 3-month ₦50,000 loan the two methods are close, but for the 12-month ₦500,000 loan the flat-rate borrower pays substantially more in interest than the reducing-balance borrower for an identical stated rate. See the 'Savings with Reducing' column on the Scenario Comparison sheet for exact naira figures, which recalculate automatically if the rate, principal or term change.</t>
-  </si>
-  <si>
     <t>2. Why this matters for disclosure</t>
   </si>
   <si>
-    <t>A flat 4%-per-month rate is NOT equivalent to a 4%-per-month reducing rate — its true (effective) cost is roughly double, because interest keeps accruing on principal already repaid. Any borrower comparing loans by headline rate alone will underestimate a flat-rate loan's real cost. The 'Effective Cost (% of principal)' columns quantify this: they show total interest-plus-fees as a percentage of the amount borrowed for each method, making the two directly comparable regardless of term.</t>
-  </si>
-  <si>
     <t>3. Affordability implications</t>
   </si>
   <si>
@@ -276,6 +270,12 @@
   </si>
   <si>
     <t>All 10 loans in the portfolio passed validation (see 'Loan Data &amp; Validation', column M): principal, fee, rate, term and disbursement date are all present and within sensible bounds, and every given Total Installment figure reconciles exactly with the flat-rate formula (Principal + Principal×Monthly Rate×Term + Fee). No missing or inconsistent entries were found; if new loans are appended below row 24 with bad data, the validation flag and conditional-formatting highlight will catch them automatically.</t>
+  </si>
+  <si>
+    <t>Across all three scenarios, the flat-rate method costs noticeably more than reducing balance for the same nominal 30% annual (3% monthly) rate, because flat-rate interest is charged every month on the full original principal, while reducing-balance interest is charged only on the shrinking outstanding balance. The gap grows with the loan term: for the 3-month ₦50,000 loan the two methods are close, but for the 12-month ₦500,000 loan the flat-rate borrower pays substantially more in interest than the reducing-balance borrower for an identical stated rate. See the 'Savings with Reducing' column on the Scenario Comparison sheet for exact naira figures, which recalculate automatically if the rate, principal or term change.</t>
+  </si>
+  <si>
+    <t>A flat 3%-per-month rate is NOT equivalent to a 3%-per-month reducing rate; its true (effective) cost is roughly double, because interest keeps accruing on principal already repaid. Any borrower comparing loans by headline rate alone will underestimate a flat-rate loan's real cost. The 'Effective Cost (% of principal)' columns quantify this: they show total interest-plus-fees as a percentage of the amount borrowed for each method, making the two directly comparable regardless of term.</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1255,7 @@
         <v>0.3</v>
       </c>
       <c r="E11" s="11">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F11" s="12">
         <v>45851</v>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="J11" s="36">
         <f t="shared" si="1"/>
-        <v>653000</v>
+        <v>655000</v>
       </c>
       <c r="K11" t="s">
         <v>49</v>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="G32" s="67">
         <f>'Loan Tracker'!E11</f>
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H32" s="68">
         <f>E32+F32</f>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="I32" s="68">
         <f>E32+F32+G32</f>
-        <v>57166.666666666664</v>
+        <v>59166.666666666664</v>
       </c>
       <c r="J32" s="68">
         <f>D32-E32</f>
@@ -4087,15 +4087,15 @@
       </c>
       <c r="E4" s="39">
         <f>'Loan Tracker'!E11</f>
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F4" s="31">
         <f>B4+(B4*D4*C4)+E4</f>
-        <v>653000</v>
+        <v>655000</v>
       </c>
       <c r="G4" s="31">
         <f>(-PMT(D4,C4,B4))*C4+E4</f>
-        <v>587922.76193002763</v>
+        <v>589922.76193002763</v>
       </c>
       <c r="H4" s="32">
         <f>F4-G4</f>
@@ -4214,19 +4214,19 @@
       </c>
       <c r="D10" s="31">
         <f>F4-B4</f>
-        <v>153000</v>
+        <v>155000</v>
       </c>
       <c r="E10" s="31">
         <f>G4-B4</f>
-        <v>87922.761930027627</v>
+        <v>89922.761930027627</v>
       </c>
       <c r="F10" s="52">
         <f>D10/B4</f>
-        <v>0.30599999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="G10" s="52">
         <f>E10/B4</f>
-        <v>0.17584552386005525</v>
+        <v>0.17984552386005526</v>
       </c>
       <c r="H10"/>
       <c r="M10"/>
@@ -4243,6 +4243,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4266,47 +4267,47 @@
     </row>
     <row r="4" spans="1:1" ht="87.5">
       <c r="A4" s="55" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5">
       <c r="A6" s="54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="62.5">
       <c r="A7" s="55" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.5">
       <c r="A9" s="54" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="87.5">
       <c r="A10" s="55" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.5">
       <c r="A12" s="54" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="62.5">
       <c r="A13" s="55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.5">
       <c r="A15" s="54" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="409.5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="50">
       <c r="A16" s="55" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
